--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E648966F-DBFC-44CE-8C2F-C6BA582BA6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7CC0D8-E93F-42CC-984D-1C5F21DC4667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="108">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -650,6 +650,21 @@
   </si>
   <si>
     <t xml:space="preserve">npm install </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git repository作成</t>
+    <rPh sb="14" eb="16">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git commit &amp; push</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>amplifyでbuild deploy</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1114,7 +1129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="2" width="2.5625" customWidth="1"/>
@@ -1776,14 +1791,29 @@
         <v>102</v>
       </c>
     </row>
-    <row r="145" spans="5:5">
+    <row r="145" spans="3:5">
       <c r="E145" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="146" spans="5:5">
+    <row r="146" spans="3:5">
       <c r="E146" t="s">
         <v>103</v>
+      </c>
+    </row>
+    <row r="148" spans="3:5">
+      <c r="C148" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="150" spans="3:5">
+      <c r="C150" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="152" spans="3:5">
+      <c r="C152" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7CC0D8-E93F-42CC-984D-1C5F21DC4667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E079EE-D99F-4BCB-B3DB-72F4EEAE6835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="全体図" sheetId="2" r:id="rId1"/>
+    <sheet name="task manager" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="137">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -665,6 +666,146 @@
   </si>
   <si>
     <t>amplifyでbuild deploy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3. CORS設定の更新</t>
+  </si>
+  <si>
+    <t>未</t>
+    <rPh sb="0" eb="1">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Table</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tasks</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskCases</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskCounters</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>採番</t>
+    <rPh sb="0" eb="2">
+      <t>サイバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>案件(=client)</t>
+    <rPh sb="0" eb="2">
+      <t>アンケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タスク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pk=taskid,fk=customerName(Case), タスク名、ステータス、日時、担当・・・</t>
+    <rPh sb="36" eb="37">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>frontend/src/app.py</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MCP(API)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git &amp; amplify</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cognito</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下に統合（案）</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウゴウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JTMTasks</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JTMClients</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JTMAgentJobs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>receipt-agent-jobs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskCasesとreceipt-agent-clients</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>task-manager</t>
+  </si>
+  <si>
+    <t>task-list-display</t>
+  </si>
+  <si>
+    <t>task-manager（DynamoDBベースのタスク管理MCP）を使ってタスクリストの表示・新規作成・更新を行</t>
+  </si>
+  <si>
+    <t>Connector</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>gmail-taskstatus</t>
+  </si>
+  <si>
+    <t>task-managerで管理しているタスクについて、関連するGmailの新着メールを検出し、 タスクのステータスを自動更新する</t>
+  </si>
+  <si>
+    <t>ツール：search_customer_names、get_task、create_task, update_task</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ClientCode(PK), ClientDesc, TaskCode(PK), TaskDesc,  TaskGroup, TaskStatus:[{Timeframe, TimeFrameStatus:[Status, UpdateDate, Assignee}]、History。　　Dependencyは削除、</t>
+    <rPh sb="157" eb="159">
+      <t>サクジョ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1128,8 +1269,174 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21C8545-CCCA-406D-B25F-807FCEF73AE6}">
+  <dimension ref="B2:G30"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <cols>
+    <col min="1" max="3" width="2.5625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7">
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7">
+      <c r="C3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7">
+      <c r="C4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="C5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="C8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="C9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="C10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="C11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7">
+      <c r="B15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7">
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="C18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="C21" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="C22" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="C25" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="C28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="C29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" t="s">
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="2" width="2.5625" customWidth="1"/>
@@ -1791,29 +2098,37 @@
         <v>102</v>
       </c>
     </row>
-    <row r="145" spans="3:5">
+    <row r="145" spans="1:5">
       <c r="E145" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="146" spans="3:5">
+    <row r="146" spans="1:5">
       <c r="E146" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="148" spans="3:5">
+    <row r="148" spans="1:5">
       <c r="C148" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="150" spans="3:5">
+    <row r="150" spans="1:5">
       <c r="C150" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="152" spans="3:5">
+    <row r="152" spans="1:5">
       <c r="C152" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" t="s">
+        <v>109</v>
+      </c>
+      <c r="C156" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E079EE-D99F-4BCB-B3DB-72F4EEAE6835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89B685D-A130-4185-9394-F6F0CDEB2EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89B685D-A130-4185-9394-F6F0CDEB2EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728CFAD5-E4E8-4FEB-BD5A-2E0C06CC0F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体図" sheetId="2" r:id="rId1"/>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728CFAD5-E4E8-4FEB-BD5A-2E0C06CC0F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1636DE-34FA-45E9-B5C9-2A1D5DB8C61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="138">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -475,16 +475,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Web UI用 API作成</t>
-    <rPh sb="6" eb="7">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>src_api/app.py</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -534,13 +524,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>coginito user登録</t>
-    <rPh sb="13" eb="15">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>aws cognito-idp admin-create-user `</t>
   </si>
   <si>
@@ -806,6 +789,44 @@
     <rPh sb="157" eb="159">
       <t>サクジョ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">sam build </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF14181F"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0051C2"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>use-container</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>API</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>coginito user</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -813,7 +834,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -893,8 +914,26 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF14181F"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0051C2"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -904,6 +943,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -921,7 +966,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -940,6 +985,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1278,34 +1325,34 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="2:7">
       <c r="C3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="2:7">
       <c r="C4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="C5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -1318,39 +1365,39 @@
     </row>
     <row r="8" spans="2:7">
       <c r="C8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="2:7">
       <c r="C9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="2:7">
       <c r="C10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="2:7">
       <c r="C11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="2:7">
       <c r="B15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="2:7">
@@ -1358,7 +1405,7 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="2:6">
@@ -1376,43 +1423,43 @@
     </row>
     <row r="20" spans="2:6">
       <c r="B20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="2:6">
       <c r="C21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="C22" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F22" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="C25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="C28" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="2:6">
@@ -1420,12 +1467,12 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1447,8 +1494,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" s="9" customFormat="1">
+      <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1463,7 +1510,8 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="C6" t="s">
+      <c r="A6" s="10"/>
+      <c r="C6" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1477,8 +1525,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
+    <row r="9" spans="1:5" s="9" customFormat="1">
+      <c r="A9" s="11" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1715,13 +1763,15 @@
       </c>
     </row>
     <row r="57" spans="1:4">
+      <c r="A57" s="10"/>
       <c r="D57" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="D58" t="s">
-        <v>26</v>
+      <c r="A58" s="10"/>
+      <c r="D58" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1730,7 +1780,8 @@
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="D60" t="s">
+      <c r="A60" s="10"/>
+      <c r="D60" s="2" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1786,8 +1837,8 @@
       </c>
     </row>
     <row r="72" spans="1:5" s="9" customFormat="1">
-      <c r="A72" t="s">
-        <v>64</v>
+      <c r="A72" s="9" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1797,15 +1848,15 @@
     </row>
     <row r="74" spans="1:5">
       <c r="B74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="B75" t="s">
+        <v>65</v>
+      </c>
+      <c r="E75" t="s">
         <v>66</v>
-      </c>
-      <c r="E75" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1828,12 +1879,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="81" spans="3:8">
+    <row r="81" spans="1:8">
       <c r="D81" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="82" spans="3:8">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="E82" t="s">
         <v>10</v>
       </c>
@@ -1841,7 +1892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="3:8">
+    <row r="83" spans="1:8">
       <c r="E83" t="s">
         <v>13</v>
       </c>
@@ -1849,7 +1900,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="3:8">
+    <row r="84" spans="1:8">
       <c r="E84" s="1" t="s">
         <v>15</v>
       </c>
@@ -1857,7 +1908,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="3:8">
+    <row r="85" spans="1:8">
       <c r="E85" t="s">
         <v>16</v>
       </c>
@@ -1865,7 +1916,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="3:8">
+    <row r="86" spans="1:8">
       <c r="E86" t="s">
         <v>17</v>
       </c>
@@ -1873,7 +1924,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="3:8">
+    <row r="87" spans="1:8">
       <c r="E87" t="s">
         <v>19</v>
       </c>
@@ -1881,7 +1932,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="3:8">
+    <row r="88" spans="1:8">
       <c r="E88" t="s">
         <v>20</v>
       </c>
@@ -1889,7 +1940,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="3:8">
+    <row r="89" spans="1:8">
       <c r="E89" t="s">
         <v>22</v>
       </c>
@@ -1897,238 +1948,240 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="3:8">
+    <row r="90" spans="1:8">
       <c r="E90" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H90" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="92" spans="3:8">
-      <c r="C92" t="s">
+    <row r="92" spans="1:8" s="9" customFormat="1">
+      <c r="A92" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="D93" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="E94" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="E95" t="s">
         <v>71</v>
       </c>
-      <c r="E92" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="93" spans="3:8">
-      <c r="D93" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="94" spans="3:8">
-      <c r="E94" t="s">
+    </row>
+    <row r="96" spans="1:8">
+      <c r="E96" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="95" spans="3:8">
-      <c r="E95" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="96" spans="3:8">
-      <c r="E96" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="97" spans="5:5">
       <c r="E97" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="98" spans="5:5">
       <c r="E98" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99" spans="5:5">
       <c r="E99" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100" spans="5:5">
       <c r="E100" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="102" spans="5:5">
       <c r="E102" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103" spans="5:5">
       <c r="E103" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="104" spans="5:5">
       <c r="E104" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="105" spans="5:5">
       <c r="E105" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="106" spans="5:5">
       <c r="E106" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="114" spans="5:5">
       <c r="E114" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="115" spans="5:5">
       <c r="E115" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="116" spans="5:5">
       <c r="E116" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="117" spans="5:5">
       <c r="E117" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="118" spans="5:5">
       <c r="E118" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="120" spans="5:5">
       <c r="E120" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="121" spans="5:5">
       <c r="E121" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="122" spans="5:5">
       <c r="E122" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="123" spans="5:5">
       <c r="E123" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="124" spans="5:5">
       <c r="E124" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="125" spans="5:5">
       <c r="E125" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="127" spans="5:5">
       <c r="E127" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="128" spans="5:5">
       <c r="E128" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="D130" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="E131" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="E132" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="E133" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="E134" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="E136" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="E138" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="E139" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="141" spans="1:5" s="9" customFormat="1">
-      <c r="A141" t="s">
-        <v>100</v>
+      <c r="A141" s="11" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="C143" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="E144" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="E145" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="E146" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="C148" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="10"/>
+      <c r="C150" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="10"/>
+      <c r="C152" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
-      <c r="C150" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
-      <c r="C152" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C156" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1636DE-34FA-45E9-B5C9-2A1D5DB8C61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F84B40-233B-4C8C-B9DB-6D40AF67B4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F84B40-233B-4C8C-B9DB-6D40AF67B4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709528E3-223F-4810-926D-00736D897AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="139">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -827,6 +827,10 @@
   </si>
   <si>
     <t>coginito user</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>?</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1011,14 +1015,14 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>19051</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>476330</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>188077</xdr:rowOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>188078</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1483,7 +1487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H156"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="2" width="2.5625" customWidth="1"/>
@@ -1785,132 +1789,132 @@
         <v>34</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="21.75">
-      <c r="C62" s="4" t="s">
+    <row r="61" spans="1:4">
+      <c r="C61" t="s">
+        <v>138</v>
+      </c>
+      <c r="D61" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="21.75">
+      <c r="C63" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
-      <c r="C63" t="s">
+    <row r="64" spans="1:4">
+      <c r="C64" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
-      <c r="C64" s="5" t="s">
+    <row r="65" spans="1:5">
+      <c r="C65" s="5" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="C65" s="6" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="C66" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="C67" s="6" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="C67" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="C68" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="C69" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="C70" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
-      <c r="C70" s="6" t="s">
+    <row r="71" spans="1:5">
+      <c r="C71" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="72" spans="1:5" s="9" customFormat="1">
-      <c r="A72" s="9" t="s">
+    <row r="73" spans="1:5" s="9" customFormat="1">
+      <c r="A73" s="9" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="B73" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="B74" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="B75" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="B76" t="s">
         <v>65</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E76" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
-      <c r="C77" t="s">
+    <row r="78" spans="1:5">
+      <c r="C78" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
-      <c r="D78" s="2" t="s">
+    <row r="79" spans="1:5">
+      <c r="D79" s="2" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="D79" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="D80" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="D81" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="D82" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="E82" t="s">
-        <v>10</v>
-      </c>
-      <c r="G82" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="E83" t="s">
+        <v>10</v>
+      </c>
+      <c r="G83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="E84" t="s">
         <v>13</v>
       </c>
-      <c r="G83" t="s">
+      <c r="G84" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
-      <c r="E84" s="1" t="s">
+    <row r="85" spans="1:8">
+      <c r="E85" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="G84" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="E85" t="s">
-        <v>16</v>
       </c>
       <c r="G85" t="s">
         <v>14</v>
@@ -1918,276 +1922,284 @@
     </row>
     <row r="86" spans="1:8">
       <c r="E86" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G86" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="E87" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G87" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="E88" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G88" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="E89" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G89" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="E90" t="s">
+        <v>22</v>
+      </c>
+      <c r="G90" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="E91" t="s">
         <v>68</v>
       </c>
-      <c r="H90" t="s">
+      <c r="H91" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="92" spans="1:8" s="9" customFormat="1">
-      <c r="A92" s="9" t="s">
+    <row r="93" spans="1:8" s="9" customFormat="1">
+      <c r="A93" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E92" s="9" t="s">
+      <c r="E93" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
-      <c r="D93" t="s">
+    <row r="94" spans="1:8">
+      <c r="D94" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="E94" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="E95" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="E96" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="97" spans="5:5">
       <c r="E97" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="98" spans="5:5">
       <c r="E98" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="99" spans="5:5">
       <c r="E99" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="5:5">
       <c r="E100" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="101" spans="5:5">
+      <c r="E101" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="102" spans="5:5">
-      <c r="E102" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="103" spans="5:5">
       <c r="E103" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104" spans="5:5">
       <c r="E104" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="105" spans="5:5">
       <c r="E105" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="106" spans="5:5">
       <c r="E106" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="107" spans="5:5">
+      <c r="E107" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="114" spans="5:5">
-      <c r="E114" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="115" spans="5:5">
       <c r="E115" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="116" spans="5:5">
       <c r="E116" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="117" spans="5:5">
       <c r="E117" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="118" spans="5:5">
       <c r="E118" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="119" spans="5:5">
+      <c r="E119" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="120" spans="5:5">
-      <c r="E120" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="121" spans="5:5">
       <c r="E121" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="122" spans="5:5">
       <c r="E122" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="123" spans="5:5">
       <c r="E123" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="124" spans="5:5">
       <c r="E124" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="125" spans="5:5">
       <c r="E125" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="126" spans="5:5">
+      <c r="E126" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="127" spans="5:5">
-      <c r="E127" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="128" spans="5:5">
       <c r="E128" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="E129" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
-      <c r="D130" t="s">
+    <row r="131" spans="1:5">
+      <c r="D131" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="E131" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="E132" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="E133" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="E134" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="E135" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
-      <c r="E136" t="s">
+    <row r="137" spans="1:5">
+      <c r="E137" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="E138" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="E139" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="E140" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="141" spans="1:5" s="9" customFormat="1">
-      <c r="A141" s="11" t="s">
+    <row r="142" spans="1:5" s="9" customFormat="1">
+      <c r="A142" s="11" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
-      <c r="C143" t="s">
+    <row r="144" spans="1:5">
+      <c r="C144" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="E144" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="E145" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="E146" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="E147" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
-      <c r="C148" t="s">
+    <row r="149" spans="1:5">
+      <c r="C149" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
-      <c r="A150" s="10"/>
-      <c r="C150" t="s">
+    <row r="151" spans="1:5">
+      <c r="A151" s="10"/>
+      <c r="C151" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
-      <c r="A152" s="10"/>
-      <c r="C152" t="s">
+    <row r="153" spans="1:5">
+      <c r="A153" s="10"/>
+      <c r="C153" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
-      <c r="A156" t="s">
+    <row r="157" spans="1:5">
+      <c r="A157" t="s">
         <v>107</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C157" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="E68" r:id="rId1" xr:uid="{6779DE2A-DCC0-4F58-8418-AF9B609FD587}"/>
+    <hyperlink ref="E69" r:id="rId1" xr:uid="{6779DE2A-DCC0-4F58-8418-AF9B609FD587}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709528E3-223F-4810-926D-00736D897AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA109D78-C8E3-454E-96AC-93542AF37D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体図" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="141">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -725,31 +725,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>以下に統合（案）</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>トウゴウ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>アン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>JTMTasks</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>JTMClients</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>JTMAgentJobs</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>receipt-agent-jobs</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -830,7 +805,63 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>?</t>
+    <r>
+      <t xml:space="preserve">sam deploy </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF14181F"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>parameter-overrides McpAuthToken=EP4wbDlMXeBN2fzGJ7K3LskVctATm09S</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskClients</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskAgentJobs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下に統合</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskFrame</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskSeries</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TaskHistory</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1321,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21C8545-CCCA-406D-B25F-807FCEF73AE6}">
-  <dimension ref="B2:G30"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="3" width="2.5625" customWidth="1"/>
@@ -1369,113 +1400,128 @@
     </row>
     <row r="8" spans="2:7">
       <c r="C8" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="2:7">
       <c r="C9" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F9" t="s">
         <v>109</v>
       </c>
       <c r="G9" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="2:7">
       <c r="C10" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="F10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="2:7">
       <c r="C11" t="s">
-        <v>123</v>
-      </c>
-      <c r="F11" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7">
-      <c r="B15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="C12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="C13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7">
+      <c r="C14" t="s">
+        <v>136</v>
+      </c>
+      <c r="F14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="2:7">
-      <c r="C16" t="s">
+    <row r="19" spans="2:6">
+      <c r="C19" t="s">
         <v>11</v>
       </c>
-      <c r="F16" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="C17" t="s">
+      <c r="F19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="C20" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="C18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="21" spans="2:6">
       <c r="C21" t="s">
-        <v>128</v>
-      </c>
-      <c r="F21" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="C22" t="s">
-        <v>131</v>
-      </c>
-      <c r="F22" t="s">
-        <v>132</v>
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="2:6">
-      <c r="B24" t="s">
-        <v>130</v>
+      <c r="C24" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="C25" t="s">
         <v>127</v>
       </c>
+      <c r="F25" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="C28" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="C29" t="s">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="C31" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="C32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1775,7 +1821,7 @@
     <row r="58" spans="1:4">
       <c r="A58" s="10"/>
       <c r="D58" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1784,17 +1830,14 @@
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="10"/>
       <c r="D60" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="C61" t="s">
-        <v>138</v>
-      </c>
-      <c r="D61" t="s">
-        <v>30</v>
+      <c r="A61" s="10"/>
+      <c r="D61" s="2" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="21.75">
@@ -1850,7 +1893,7 @@
     </row>
     <row r="73" spans="1:5" s="9" customFormat="1">
       <c r="A73" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1970,7 +2013,7 @@
     </row>
     <row r="93" spans="1:8" s="9" customFormat="1">
       <c r="A93" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>69</v>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA109D78-C8E3-454E-96AC-93542AF37D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9BD1C83-365A-4568-B536-2C3FD6948C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体図" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="146">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -862,6 +862,23 @@
   </si>
   <si>
     <t>TaskHistory</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aws secretsmanager create-secret `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --name receipt-agent/task-mcp-server `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --secret-string '{"url":"&lt;TaskMcpFunctionUrlの値&gt;","auth_token":"&lt;McpAuthTokenの値&gt;"}' `</t>
+  </si>
+  <si>
+    <t>secret</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  --secret-string '{"url":"&lt;TaskMcpFunctionUrlの値&gt;","auth_token":"&lt;McpAuthTokenの値&gt;"}' `</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1046,14 +1063,14 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>19051</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>476330</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>188078</xdr:rowOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>188077</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1533,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:M166"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="2" width="2.5625" customWidth="1"/>
@@ -1850,22 +1867,22 @@
         <v>53</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:13">
       <c r="C65" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:13">
       <c r="C66" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:13">
       <c r="C67" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:13">
       <c r="C68" s="5" t="s">
         <v>59</v>
       </c>
@@ -1873,7 +1890,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:13">
       <c r="C69" s="5" t="s">
         <v>61</v>
       </c>
@@ -1881,32 +1898,32 @@
         <v>62</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:13">
       <c r="C70" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:13">
       <c r="C71" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="73" spans="1:5" s="9" customFormat="1">
+    <row r="73" spans="1:13" s="9" customFormat="1">
       <c r="A73" s="9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:13">
       <c r="B74" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:13">
       <c r="B75" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:13">
       <c r="B76" t="s">
         <v>65</v>
       </c>
@@ -1914,32 +1931,44 @@
         <v>66</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:13">
       <c r="C78" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="79" spans="1:5">
+      <c r="M78" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
       <c r="D79" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="80" spans="1:5">
+      <c r="M79" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13">
       <c r="D80" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="81" spans="1:8">
+      <c r="M80" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="81" spans="3:13">
       <c r="D81" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="82" spans="1:8">
+      <c r="M81" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13">
       <c r="D82" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="3:13">
       <c r="E83" t="s">
         <v>10</v>
       </c>
@@ -1947,7 +1976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="3:13">
       <c r="E84" t="s">
         <v>13</v>
       </c>
@@ -1955,7 +1984,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="3:13">
       <c r="E85" s="1" t="s">
         <v>15</v>
       </c>
@@ -1963,7 +1992,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="3:13">
       <c r="E86" t="s">
         <v>16</v>
       </c>
@@ -1971,7 +2000,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="3:13">
       <c r="E87" t="s">
         <v>17</v>
       </c>
@@ -1979,7 +2008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="3:13">
       <c r="E88" t="s">
         <v>19</v>
       </c>
@@ -1987,7 +2016,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="3:13">
       <c r="E89" t="s">
         <v>20</v>
       </c>
@@ -1995,7 +2024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="3:13">
       <c r="E90" t="s">
         <v>22</v>
       </c>
@@ -2003,7 +2032,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="3:13">
       <c r="E91" t="s">
         <v>68</v>
       </c>
@@ -2011,231 +2040,256 @@
         <v>29</v>
       </c>
     </row>
-    <row r="93" spans="1:8" s="9" customFormat="1">
-      <c r="A93" s="9" t="s">
+    <row r="92" spans="3:13">
+      <c r="C92" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13">
+      <c r="D93" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13">
+      <c r="D94" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13">
+      <c r="D95" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="96" spans="3:13">
+      <c r="D96" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" s="9" customFormat="1">
+      <c r="A102" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E93" s="9" t="s">
+      <c r="E102" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
-      <c r="D94" t="s">
+    <row r="103" spans="1:5">
+      <c r="D103" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
-      <c r="E95" t="s">
+    <row r="104" spans="1:5">
+      <c r="E104" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
-      <c r="E96" t="s">
+    <row r="105" spans="1:5">
+      <c r="E105" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="97" spans="5:5">
-      <c r="E97" t="s">
+    <row r="106" spans="1:5">
+      <c r="E106" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="98" spans="5:5">
-      <c r="E98" t="s">
+    <row r="107" spans="1:5">
+      <c r="E107" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="99" spans="5:5">
-      <c r="E99" t="s">
+    <row r="108" spans="1:5">
+      <c r="E108" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="100" spans="5:5">
-      <c r="E100" t="s">
+    <row r="109" spans="1:5">
+      <c r="E109" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="101" spans="5:5">
-      <c r="E101" t="s">
+    <row r="110" spans="1:5">
+      <c r="E110" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="103" spans="5:5">
-      <c r="E103" t="s">
+    <row r="112" spans="1:5">
+      <c r="E112" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="104" spans="5:5">
-      <c r="E104" t="s">
+    <row r="113" spans="5:5">
+      <c r="E113" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="105" spans="5:5">
-      <c r="E105" t="s">
+    <row r="114" spans="5:5">
+      <c r="E114" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row r="106" spans="5:5">
-      <c r="E106" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="107" spans="5:5">
-      <c r="E107" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="115" spans="5:5">
       <c r="E115" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="116" spans="5:5">
       <c r="E116" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="117" spans="5:5">
-      <c r="E117" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="118" spans="5:5">
-      <c r="E118" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="119" spans="5:5">
-      <c r="E119" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="121" spans="5:5">
-      <c r="E121" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="122" spans="5:5">
-      <c r="E122" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="123" spans="5:5">
-      <c r="E123" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="124" spans="5:5">
       <c r="E124" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="125" spans="5:5">
       <c r="E125" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="126" spans="5:5">
       <c r="E126" t="s">
-        <v>84</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="127" spans="5:5">
+      <c r="E127" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="128" spans="5:5">
       <c r="E128" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="130" spans="4:5">
+      <c r="E130" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="131" spans="4:5">
+      <c r="E131" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="132" spans="4:5">
+      <c r="E132" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="133" spans="4:5">
+      <c r="E133" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="134" spans="4:5">
+      <c r="E134" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="135" spans="4:5">
+      <c r="E135" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="137" spans="4:5">
+      <c r="E137" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
-      <c r="E129" t="s">
+    <row r="138" spans="4:5">
+      <c r="E138" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
-      <c r="D131" t="s">
+    <row r="140" spans="4:5">
+      <c r="D140" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
-      <c r="E132" t="s">
+    <row r="141" spans="4:5">
+      <c r="E141" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
-      <c r="E133" t="s">
+    <row r="142" spans="4:5">
+      <c r="E142" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
-      <c r="E134" t="s">
+    <row r="143" spans="4:5">
+      <c r="E143" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
-      <c r="E135" t="s">
+    <row r="144" spans="4:5">
+      <c r="E144" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="E137" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
-      <c r="E139" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="E140" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" s="9" customFormat="1">
-      <c r="A142" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="C144" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="E145" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="E146" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="E148" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="E149" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" s="9" customFormat="1">
+      <c r="A151" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="C153" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="E154" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="E155" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
-      <c r="E147" t="s">
+    <row r="156" spans="1:5">
+      <c r="E156" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
-      <c r="C149" t="s">
+    <row r="158" spans="1:5">
+      <c r="C158" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
-      <c r="A151" s="10"/>
-      <c r="C151" t="s">
+    <row r="160" spans="1:5">
+      <c r="A160" s="10"/>
+      <c r="C160" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
-      <c r="A153" s="10"/>
-      <c r="C153" t="s">
+    <row r="162" spans="1:3">
+      <c r="A162" s="10"/>
+      <c r="C162" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
-      <c r="A157" t="s">
+    <row r="166" spans="1:3">
+      <c r="A166" t="s">
         <v>107</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C166" t="s">
         <v>106</v>
       </c>
     </row>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9BD1C83-365A-4568-B536-2C3FD6948C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8813AF9C-3F6B-4300-BAE0-5E95D2DD0CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体図" sheetId="2" r:id="rId1"/>
     <sheet name="task manager" sheetId="1" r:id="rId2"/>
+    <sheet name="agent" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="238">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -881,12 +882,439 @@
     <t xml:space="preserve">  --secret-string '{"url":"&lt;TaskMcpFunctionUrlの値&gt;","auth_token":"&lt;McpAuthTokenの値&gt;"}' `</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>以下旧情報</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>キュウジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>task managerに統合一元化　（taskmanager, task-mcp-server, agentmanager)</t>
+    <rPh sb="13" eb="15">
+      <t>トウゴウ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>イチゲンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>deploy手順はread.me</t>
+    <rPh sb="6" eb="8">
+      <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MCP Function URL</t>
+  </si>
+  <si>
+    <t>https://v5ofxfmo2tokwlsukn2io7f27m0stmmr.lambda-url.ap-northeast-1.on.aws/</t>
+  </si>
+  <si>
+    <t>Web APIエンドポイント</t>
+  </si>
+  <si>
+    <t>MCP Bearerトークン</t>
+  </si>
+  <si>
+    <t>https://kvwrqkhd29.execute-api.ap-northeast-1.amazonaws.com（フロントエンド用、config.js更新済み）</t>
+  </si>
+  <si>
+    <t>変更なし</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sam</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>共通CRUD関数, api, mcp</t>
+    <rPh sb="0" eb="2">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ui</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git commit&amp;push &gt; amplify deploy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>agentデプロイ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>agentmanagerから移植</t>
+    <rPh sb="14" eb="16">
+      <t>イショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cd C:\Users\woody\0woodyprojects\taskmanager\task-agent</t>
+  </si>
+  <si>
+    <t>1. 共有モジュールのコピー(必須・毎回)</t>
+  </si>
+  <si>
+    <t>2. agentcore configure / launch</t>
+  </si>
+  <si>
+    <t>agentcore launch</t>
+  </si>
+  <si>
+    <t>3. IAM権限の追加</t>
+  </si>
+  <si>
+    <t>aws iam put-role-policy `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --policy-name task-agent-secrets-usertoken `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --policy-document file://secrets-access-policy-usertoken.json</t>
+  </si>
+  <si>
+    <t>4. 環境変数の設定</t>
+  </si>
+  <si>
+    <t>TASKS_TABLE=Tasks</t>
+  </si>
+  <si>
+    <t>CLIENTS_TABLE=TaskClients</t>
+  </si>
+  <si>
+    <t>SERIES_TABLE=TaskSeries</t>
+  </si>
+  <si>
+    <t>FRAMES_TABLE=TaskFrames</t>
+  </si>
+  <si>
+    <t>HISTORY_TABLE=TaskHistory</t>
+  </si>
+  <si>
+    <t>AGENT_JOBS_TABLE=TaskAgentJob</t>
+  </si>
+  <si>
+    <t>task_repository.pyはモジュールロード時に以下6つの環境変数を必須参照します。新runtimeに設定してください(具体的な設定方法はagentcore configure --helpのenv系オプション、またはAWSコンソール「Bedrock AgentCore → Runtime → 環境変数」から。CLIのバージョンによりフラグ名が異なる可能性があるため、agentcore launch --helpで確認してください):</t>
+  </si>
+  <si>
+    <t>5. Secrets Manager: 新シークレット作成</t>
+  </si>
+  <si>
+    <t>既存の値をそのままコピーして新しい名前で登録します。</t>
+  </si>
+  <si>
+    <t>6. 新runtime単体の動作確認</t>
+  </si>
+  <si>
+    <t>aws bedrock-agentcore invoke-agent-runtime `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --region ap-northeast-1 `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  output.json</t>
+  </si>
+  <si>
+    <t>7. taskmanagerスタック側の更新</t>
+  </si>
+  <si>
+    <t>cd C:\Users\woody\0woodyprojects\taskmanager</t>
+  </si>
+  <si>
+    <t>8. Web UIでのエンドツーエンド確認</t>
+  </si>
+  <si>
+    <t>9. 旧環境の後片付け(動作確認が取れてから)</t>
+  </si>
+  <si>
+    <t>template.yamlのAgentRuntimeArnデフォルト値を新ARNに更新し(またはデプロイ時パラメータで上書き)、taskmanagerスタックを再デプロイします。</t>
+  </si>
+  <si>
+    <t>(前回移行時の10-2節のトラブル対応 — Norton証明書/AWS_CA_BUNDLE、--use-containerが必要なpywin32問題 — が再発する可能性があります。設計書10-2節を参照してください)</t>
+  </si>
+  <si>
+    <t>「エージェント」タブからarchivistを実行し、TaskAgentJobsテーブルでstatus=completedになること、Drive上に実際にリネーム結果が反映されることを確認します。</t>
+  </si>
+  <si>
+    <t>旧agent_agentcore runtimeをagentcore側で削除(またはAmazonBedrockAgentCoreSDKRuntime-...ロール・ECRリポジトリの整理)</t>
+  </si>
+  <si>
+    <t>不要になったreceipt-agent/task-mcp-serverシークレットを削除</t>
+  </si>
+  <si>
+    <t>agentmanager/receipt-agentディレクトリはしばらく残しておき、問題なければ削除</t>
+  </si>
+  <si>
+    <t>0. 事前準備</t>
+  </si>
+  <si>
+    <t>agentcore CLI（Bedrock AgentCore Starter Toolkit）がこのマシンに入っていればそのまま使えます（agentmanager/receipt-agentで使用済み）。</t>
+  </si>
+  <si>
+    <t>Docker Desktop起動を確認（agentcore launchはローカルDockerまたはCodeBuild経由でビルドします。既存.bedrock_agentcore.yamlにcodebuild:セクションがあるため、恐らくCodeBuild経由のクラウドビルドです）。</t>
+  </si>
+  <si>
+    <t>Copy-Item ..\layer\python\task_repository.py . -Force</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>agentcore configure --entrypoint task_agent.py --region ap-northeast-1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Agent ARN</t>
+  </si>
+  <si>
+    <t>task_agent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Agent Name</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>155830630328.dkr.ecr.ap-northeast-1.amazonaws.com/bedrock-agentcore-task_agent:20260802-005503-286</t>
+  </si>
+  <si>
+    <t>ECR URI:</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>role名は→</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">aws iam put-role-policy --role-name </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AmazonBedrockAgentCoreSDKRuntime-ap-northeast-1-b93c04ec99</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> --policy-name task-agent-dynamodb-clients --policy-document file://dynamodb-access-policy-clients.json</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  --role-name </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AmazonBedrockAgentCoreSDKRuntime-ap-northeast-1-b93c04ec99</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> `</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>agentcore launch --env TASKS_TABLE=Tasks --env CLIENTS_TABLE=TaskClients --env SERIES_TABLE=TaskSeries --env FRAMES_TABLE=TaskFrames --env HISTORY_TABLE=TaskHistory --env AGENT_JOBS_TABLE=TaskAgentJobs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>補足:</t>
+  </si>
+  <si>
+    <t>--envはKEY=VALUE形式で、複数回指定できます。task_repository.pyが起動時に必須参照する6つのテーブル名をすべて渡してください。</t>
+  </si>
+  <si>
+    <t>GOOGLE_USER_TOKEN_SECRET_NAMEはコード側デフォルトが既にtask-agent/google-drive-user-tokenになっているため、そのシークレットさえ作成済みであれば--envで渡す必要はありません(まだ作成していなければ、以前案内したaws secretsmanager create-secret --name task-agent/google-drive-user-token ...を先に実行してください)。</t>
+  </si>
+  <si>
+    <t>既に一度agentcore launchしていて更新の場合は、ConflictExceptionで失敗することがあります。その場合は--auto-update-on-conflict(-auc)を追加してください。</t>
+  </si>
+  <si>
+    <t>aws secretsmanager get-secret-value --secret-id receipt-agent/google-drive-user-token --query SecretString --output text | Out-File -Encoding utf8 tmp-token.json</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aws secretsmanager create-secret --region ap-northeast-1 --name task-agent/google-drive-user-token --secret-string (Get-Content tmp-token.json -Raw)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Remove-Item tmp-token.json</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>arn:aws:bedrock-agentcore:ap-northeast-1:155830630328:runtime/task_agent-lAAoax7UkB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>$json = '{"prompt":"IKKの登録クライアント一覧を教えて"}'</t>
+  </si>
+  <si>
+    <t>[System.IO.File]::WriteAllText("$PWD\payload.json", $json, (New-Object System.Text.UTF8Encoding($false)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --agent-runtime-arn arn:aws:bedrock-agentcore:ap-northeast-1:155830630328:runtime/task_agent-lAAoax7UkB `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --runtime-session-id ("test-session-" + [guid]::NewGuid().ToString("N")) `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --payload fileb://payload.json `</t>
+  </si>
+  <si>
+    <t>Get-Content output.json -Encoding utf8</t>
+  </si>
+  <si>
+    <t>      Bedrock AgentCore runtime ARN for the receipt-classification ("分類") agent</t>
+  </si>
+  <si>
+    <t>      (task-agent/, formerly agentmanager/receipt-agent), invoked asynchronously</t>
+  </si>
+  <si>
+    <t>      by TaskAgentJobProcessorFunction.</t>
+  </si>
+  <si>
+    <t>AgentRuntimeArn:</t>
+  </si>
+  <si>
+    <t>    Type: String</t>
+  </si>
+  <si>
+    <t>    Default: "arn:aws:bedrock-agentcore:ap-northeast-1:155830630328:runtime/task_agent-lAAoax7UkB"</t>
+  </si>
+  <si>
+    <t>    Description: &gt;</t>
+  </si>
+  <si>
+    <t>sam build --use-container</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>sam deploy --parameter-overrides AgentRuntimeArn=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>arn:aws:bedrock-agentcore:ap-northeast-1:155830630328:runtime/task_agent-lAAoax7UkB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> McpAuthToken=</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="4"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EP4wbDlMXeBN2fzGJ7K3LskVctATm09S</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aws secretsmanager describe-secret --secret-id task-agent/google-drive-user-token --region ap-northeast-1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aws secretsmanager get-secret-value --region ap-northeast-1 --secret-id task-agent/google-drive-user-token --query SecretString --output text</t>
+  </si>
+  <si>
+    <t>aws secretsmanager put-secret-value --region ap-northeast-1 --secret-id task-agent/google-drive-user-token --secret-string '&lt;出力されたJSON&gt;'</t>
+  </si>
+  <si>
+    <t>aws secretsmanager put-secret-value --region ap-northeast-1 --secret-id task-agent/google-drive-user-token --secret-string file://tmp-token.json</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>python get_refresh_token.py</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG形式</t>
+    <rPh sb="2" eb="4">
+      <t>ケイシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OK形式</t>
+    <rPh sb="2" eb="4">
+      <t>ケイシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>”がない</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -984,8 +1412,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1004,6 +1439,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF33"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1018,7 +1459,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1039,6 +1480,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1046,6 +1489,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF66FF33"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1063,13 +1511,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>19051</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>476330</xdr:colOff>
-      <xdr:row>120</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>188077</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1095,6 +1543,143 @@
         <a:xfrm>
           <a:off x="7924800" y="22679026"/>
           <a:ext cx="8029655" cy="2183564"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>585788</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>200026</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>257240</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>57584</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2BDD808-68E0-C04A-4A23-CF53DA16EE8A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12830176" y="4452939"/>
+          <a:ext cx="5843652" cy="1200583"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>33338</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>33338</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>223229</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFB1A8CD-FEF2-588B-1365-95A250C299B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1304926" y="13015913"/>
+          <a:ext cx="8453437" cy="861404"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>52387</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>52389</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>643017</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>190352</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EAB7458-5967-991E-56EC-845C29565333}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10239375" y="13034964"/>
+          <a:ext cx="8820230" cy="809476"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1550,755 +2135,1284 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M166"/>
+  <dimension ref="A1:M184"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="2" width="2.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="9" customFormat="1">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="B3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="C4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="C5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="C6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="B3" t="s">
+    <row r="9" spans="1:10">
+      <c r="C9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="C10" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="C12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="C13" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="C15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="C16" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="B17" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="C18" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="9" customFormat="1">
+      <c r="A20" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="B21" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="C4" t="s">
+    <row r="22" spans="1:5">
+      <c r="C22" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="10"/>
-      <c r="C6" s="2" t="s">
+    <row r="24" spans="1:5">
+      <c r="A24" s="10"/>
+      <c r="C24" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="B7" t="s">
+    <row r="25" spans="1:5">
+      <c r="B25" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="C8" t="s">
+    <row r="26" spans="1:5">
+      <c r="C26" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="9" customFormat="1">
-      <c r="A9" s="11" t="s">
+    <row r="27" spans="1:5" s="9" customFormat="1">
+      <c r="A27" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="C10" t="s">
+    <row r="28" spans="1:5">
+      <c r="C28" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="D11" t="s">
+    <row r="29" spans="1:5">
+      <c r="D29" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="D12" t="s">
+    <row r="30" spans="1:5">
+      <c r="D30" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="C13" t="s">
+    <row r="31" spans="1:5">
+      <c r="C31" t="s">
         <v>8</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E31" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="D14" s="3" t="s">
+    <row r="32" spans="1:5">
+      <c r="D32" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="D15" s="3" t="s">
+    <row r="33" spans="2:6">
+      <c r="D33" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:6">
-      <c r="C17" t="s">
+    <row r="35" spans="2:6">
+      <c r="C35" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
-      <c r="D18" t="s">
+    <row r="36" spans="2:6">
+      <c r="D36" t="s">
         <v>10</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F36" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="2:6">
-      <c r="D19" t="s">
+    <row r="37" spans="2:6">
+      <c r="D37" t="s">
         <v>13</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F37" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:6">
-      <c r="D20" s="1" t="s">
+    <row r="38" spans="2:6">
+      <c r="D38" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F38" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="2:6">
-      <c r="D21" t="s">
+    <row r="39" spans="2:6">
+      <c r="D39" t="s">
         <v>16</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F39" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
-      <c r="D22" t="s">
+    <row r="40" spans="2:6">
+      <c r="D40" t="s">
         <v>17</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F40" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="2:6">
-      <c r="D23" t="s">
+    <row r="41" spans="2:6">
+      <c r="D41" t="s">
         <v>19</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F41" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
-      <c r="D24" t="s">
+    <row r="42" spans="2:6">
+      <c r="D42" t="s">
         <v>20</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F42" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
-      <c r="D25" t="s">
+    <row r="43" spans="2:6">
+      <c r="D43" t="s">
         <v>22</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F43" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
-      <c r="B27" t="s">
+    <row r="45" spans="2:6">
+      <c r="B45" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="2:6">
-      <c r="D28" t="s">
+    <row r="46" spans="2:6">
+      <c r="D46" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
-      <c r="D29" t="s">
+    <row r="47" spans="2:6">
+      <c r="D47" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
-      <c r="C31" t="s">
+    <row r="49" spans="2:4">
+      <c r="C49" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
-      <c r="C32" t="s">
+    <row r="50" spans="2:4">
+      <c r="C50" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="2:4">
-      <c r="B34" t="s">
+    <row r="52" spans="2:4">
+      <c r="B52" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="2:4">
-      <c r="C35" t="s">
+    <row r="53" spans="2:4">
+      <c r="C53" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
-      <c r="D36" t="s">
+    <row r="54" spans="2:4">
+      <c r="D54" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
-      <c r="D37" t="s">
+    <row r="55" spans="2:4">
+      <c r="D55" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="2:4">
-      <c r="D38" t="s">
+    <row r="56" spans="2:4">
+      <c r="D56" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="2:4">
-      <c r="D39" t="s">
+    <row r="57" spans="2:4">
+      <c r="D57" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="2:4">
-      <c r="D40" t="s">
+    <row r="58" spans="2:4">
+      <c r="D58" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="2:4">
-      <c r="D41" t="s">
+    <row r="59" spans="2:4">
+      <c r="D59" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="2:4">
-      <c r="D42" t="s">
+    <row r="60" spans="2:4">
+      <c r="D60" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="2:4">
-      <c r="D43" t="s">
+    <row r="61" spans="2:4">
+      <c r="D61" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="2:4">
-      <c r="D44" t="s">
+    <row r="62" spans="2:4">
+      <c r="D62" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="2:4">
-      <c r="D45" t="s">
+    <row r="63" spans="2:4">
+      <c r="D63" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="2:4">
-      <c r="D46" t="s">
+    <row r="64" spans="2:4">
+      <c r="D64" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="47" spans="2:4">
-      <c r="D47" t="s">
+    <row r="65" spans="1:4">
+      <c r="D65" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="2:4">
-      <c r="D48" t="s">
+    <row r="66" spans="1:4">
+      <c r="D66" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
-      <c r="D49" t="s">
+    <row r="67" spans="1:4">
+      <c r="D67" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
-      <c r="C53" t="s">
+    <row r="71" spans="1:4">
+      <c r="C71" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
-      <c r="D54" t="s">
+    <row r="72" spans="1:4">
+      <c r="D72" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
-      <c r="D55" t="s">
+    <row r="73" spans="1:4">
+      <c r="D73" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
-      <c r="C56" t="s">
+    <row r="74" spans="1:4">
+      <c r="C74" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="10"/>
-      <c r="D57" s="2" t="s">
+    <row r="75" spans="1:4">
+      <c r="A75" s="10"/>
+      <c r="D75" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="10"/>
-      <c r="D58" s="2" t="s">
+    <row r="76" spans="1:4">
+      <c r="A76" s="10"/>
+      <c r="D76" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
-      <c r="D59" t="s">
+    <row r="77" spans="1:4">
+      <c r="D77" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
-      <c r="D60" s="2" t="s">
+    <row r="78" spans="1:4">
+      <c r="D78" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="10"/>
-      <c r="D61" s="2" t="s">
+    <row r="79" spans="1:4">
+      <c r="A79" s="10"/>
+      <c r="D79" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="21.75">
-      <c r="C63" s="4" t="s">
+    <row r="81" spans="1:13" ht="21.75">
+      <c r="C81" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
-      <c r="C64" t="s">
+    <row r="82" spans="1:13">
+      <c r="C82" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
-      <c r="C65" s="5" t="s">
+    <row r="83" spans="1:13">
+      <c r="C83" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
-      <c r="C66" s="6" t="s">
+    <row r="84" spans="1:13">
+      <c r="C84" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
-      <c r="C67" s="6" t="s">
+    <row r="85" spans="1:13">
+      <c r="C85" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
-      <c r="C68" s="5" t="s">
+    <row r="86" spans="1:13">
+      <c r="C86" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="E86" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
-      <c r="C69" s="5" t="s">
+    <row r="87" spans="1:13">
+      <c r="C87" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E87" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
-      <c r="C70" s="5" t="s">
+    <row r="88" spans="1:13">
+      <c r="C88" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
-      <c r="C71" s="6" t="s">
+    <row r="89" spans="1:13">
+      <c r="C89" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="73" spans="1:13" s="9" customFormat="1">
-      <c r="A73" s="9" t="s">
+    <row r="91" spans="1:13" s="9" customFormat="1">
+      <c r="A91" s="9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
-      <c r="B74" t="s">
+    <row r="92" spans="1:13">
+      <c r="B92" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
-      <c r="B75" t="s">
+    <row r="93" spans="1:13">
+      <c r="B93" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
-      <c r="B76" t="s">
+    <row r="94" spans="1:13">
+      <c r="B94" t="s">
         <v>65</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E94" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
-      <c r="C78" t="s">
+    <row r="96" spans="1:13">
+      <c r="C96" t="s">
         <v>36</v>
       </c>
-      <c r="M78" t="s">
+      <c r="M96" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
-      <c r="D79" s="2" t="s">
+    <row r="97" spans="3:13">
+      <c r="D97" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M79" t="s">
+      <c r="M97" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
-      <c r="D80" t="s">
+    <row r="98" spans="3:13">
+      <c r="D98" t="s">
         <v>26</v>
       </c>
-      <c r="M80" t="s">
+      <c r="M98" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="81" spans="3:13">
-      <c r="D81" t="s">
+    <row r="99" spans="3:13">
+      <c r="D99" t="s">
         <v>52</v>
       </c>
-      <c r="M81" t="s">
+      <c r="M99" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="82" spans="3:13">
-      <c r="D82" t="s">
+    <row r="100" spans="3:13">
+      <c r="D100" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="83" spans="3:13">
-      <c r="E83" t="s">
+    <row r="101" spans="3:13">
+      <c r="E101" t="s">
         <v>10</v>
       </c>
-      <c r="G83" t="s">
+      <c r="G101" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="3:13">
-      <c r="E84" t="s">
+    <row r="102" spans="3:13">
+      <c r="E102" t="s">
         <v>13</v>
       </c>
-      <c r="G84" t="s">
+      <c r="G102" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="3:13">
-      <c r="E85" s="1" t="s">
+    <row r="103" spans="3:13">
+      <c r="E103" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G103" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="3:13">
-      <c r="E86" t="s">
+    <row r="104" spans="3:13">
+      <c r="E104" t="s">
         <v>16</v>
       </c>
-      <c r="G86" t="s">
+      <c r="G104" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="3:13">
-      <c r="E87" t="s">
+    <row r="105" spans="3:13">
+      <c r="E105" t="s">
         <v>17</v>
       </c>
-      <c r="G87" t="s">
+      <c r="G105" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="3:13">
-      <c r="E88" t="s">
+    <row r="106" spans="3:13">
+      <c r="E106" t="s">
         <v>19</v>
       </c>
-      <c r="G88" t="s">
+      <c r="G106" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="89" spans="3:13">
-      <c r="E89" t="s">
+    <row r="107" spans="3:13">
+      <c r="E107" t="s">
         <v>20</v>
       </c>
-      <c r="G89" t="s">
+      <c r="G107" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="3:13">
-      <c r="E90" t="s">
+    <row r="108" spans="3:13">
+      <c r="E108" t="s">
         <v>22</v>
       </c>
-      <c r="G90" t="s">
+      <c r="G108" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="91" spans="3:13">
-      <c r="E91" t="s">
+    <row r="109" spans="3:13">
+      <c r="E109" t="s">
         <v>68</v>
       </c>
-      <c r="H91" t="s">
+      <c r="H109" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="92" spans="3:13">
-      <c r="C92" t="s">
+    <row r="110" spans="3:13">
+      <c r="C110" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="93" spans="3:13">
-      <c r="D93" t="s">
+    <row r="111" spans="3:13">
+      <c r="D111" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="94" spans="3:13">
-      <c r="D94" t="s">
+    <row r="112" spans="3:13">
+      <c r="D112" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="95" spans="3:13">
-      <c r="D95" t="s">
+    <row r="113" spans="1:5">
+      <c r="D113" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="96" spans="3:13">
-      <c r="D96" t="s">
+    <row r="114" spans="1:5">
+      <c r="D114" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="102" spans="1:5" s="9" customFormat="1">
-      <c r="A102" s="9" t="s">
+    <row r="120" spans="1:5" s="9" customFormat="1">
+      <c r="A120" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E102" s="9" t="s">
+      <c r="E120" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
-      <c r="D103" t="s">
+    <row r="121" spans="1:5">
+      <c r="D121" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
-      <c r="E104" t="s">
+    <row r="122" spans="1:5">
+      <c r="E122" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
-      <c r="E105" t="s">
+    <row r="123" spans="1:5">
+      <c r="E123" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
-      <c r="E106" t="s">
+    <row r="124" spans="1:5">
+      <c r="E124" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
-      <c r="E107" t="s">
+    <row r="125" spans="1:5">
+      <c r="E125" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
-      <c r="E108" t="s">
+    <row r="126" spans="1:5">
+      <c r="E126" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
-      <c r="E109" t="s">
+    <row r="127" spans="1:5">
+      <c r="E127" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
-      <c r="E110" t="s">
+    <row r="128" spans="1:5">
+      <c r="E128" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
-      <c r="E112" t="s">
+    <row r="130" spans="5:5">
+      <c r="E130" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="113" spans="5:5">
-      <c r="E113" t="s">
+    <row r="131" spans="5:5">
+      <c r="E131" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="114" spans="5:5">
-      <c r="E114" t="s">
+    <row r="132" spans="5:5">
+      <c r="E132" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="115" spans="5:5">
-      <c r="E115" t="s">
+    <row r="133" spans="5:5">
+      <c r="E133" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="116" spans="5:5">
-      <c r="E116" t="s">
+    <row r="134" spans="5:5">
+      <c r="E134" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="124" spans="5:5">
-      <c r="E124" t="s">
+    <row r="142" spans="5:5">
+      <c r="E142" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="125" spans="5:5">
-      <c r="E125" t="s">
+    <row r="143" spans="5:5">
+      <c r="E143" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="126" spans="5:5">
-      <c r="E126" t="s">
+    <row r="144" spans="5:5">
+      <c r="E144" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="127" spans="5:5">
-      <c r="E127" t="s">
+    <row r="145" spans="4:5">
+      <c r="E145" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="128" spans="5:5">
-      <c r="E128" t="s">
+    <row r="146" spans="4:5">
+      <c r="E146" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="130" spans="4:5">
-      <c r="E130" t="s">
+    <row r="148" spans="4:5">
+      <c r="E148" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="131" spans="4:5">
-      <c r="E131" t="s">
+    <row r="149" spans="4:5">
+      <c r="E149" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="132" spans="4:5">
-      <c r="E132" t="s">
+    <row r="150" spans="4:5">
+      <c r="E150" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="133" spans="4:5">
-      <c r="E133" t="s">
+    <row r="151" spans="4:5">
+      <c r="E151" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="134" spans="4:5">
-      <c r="E134" t="s">
+    <row r="152" spans="4:5">
+      <c r="E152" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="135" spans="4:5">
-      <c r="E135" t="s">
+    <row r="153" spans="4:5">
+      <c r="E153" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="137" spans="4:5">
-      <c r="E137" t="s">
+    <row r="155" spans="4:5">
+      <c r="E155" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="138" spans="4:5">
-      <c r="E138" t="s">
+    <row r="156" spans="4:5">
+      <c r="E156" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="140" spans="4:5">
-      <c r="D140" t="s">
+    <row r="158" spans="4:5">
+      <c r="D158" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="141" spans="4:5">
-      <c r="E141" t="s">
+    <row r="159" spans="4:5">
+      <c r="E159" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="142" spans="4:5">
-      <c r="E142" t="s">
+    <row r="160" spans="4:5">
+      <c r="E160" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="143" spans="4:5">
-      <c r="E143" t="s">
+    <row r="161" spans="1:5">
+      <c r="E161" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="144" spans="4:5">
-      <c r="E144" t="s">
+    <row r="162" spans="1:5">
+      <c r="E162" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
-      <c r="E146" t="s">
+    <row r="164" spans="1:5">
+      <c r="E164" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
-      <c r="E148" t="s">
+    <row r="166" spans="1:5">
+      <c r="E166" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
-      <c r="E149" t="s">
+    <row r="167" spans="1:5">
+      <c r="E167" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="151" spans="1:5" s="9" customFormat="1">
-      <c r="A151" s="11" t="s">
+    <row r="169" spans="1:5" s="9" customFormat="1">
+      <c r="A169" s="11" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
-      <c r="C153" t="s">
+    <row r="171" spans="1:5">
+      <c r="C171" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
-      <c r="E154" t="s">
+    <row r="172" spans="1:5">
+      <c r="E172" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
-      <c r="E155" t="s">
+    <row r="173" spans="1:5">
+      <c r="E173" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
-      <c r="E156" t="s">
+    <row r="174" spans="1:5">
+      <c r="E174" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
-      <c r="C158" t="s">
+    <row r="176" spans="1:5">
+      <c r="C176" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
-      <c r="A160" s="10"/>
-      <c r="C160" t="s">
+    <row r="178" spans="1:3">
+      <c r="A178" s="10"/>
+      <c r="C178" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
-      <c r="A162" s="10"/>
-      <c r="C162" t="s">
+    <row r="180" spans="1:3">
+      <c r="A180" s="10"/>
+      <c r="C180" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
-      <c r="A166" t="s">
+    <row r="184" spans="1:3">
+      <c r="A184" t="s">
         <v>107</v>
       </c>
-      <c r="C166" t="s">
+      <c r="C184" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="E69" r:id="rId1" xr:uid="{6779DE2A-DCC0-4F58-8418-AF9B609FD587}"/>
+    <hyperlink ref="E87" r:id="rId1" xr:uid="{6779DE2A-DCC0-4F58-8418-AF9B609FD587}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89218E65-9CD0-49A4-A7F2-71B0476A86F1}">
+  <dimension ref="A1:T105"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <cols>
+    <col min="1" max="3" width="2.5625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="B2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="D4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="D5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="D8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="12"/>
+      <c r="D9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="D12" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="12"/>
+      <c r="D13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="12"/>
+      <c r="D14" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="E15" t="s">
+        <v>200</v>
+      </c>
+      <c r="G15" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="E16" t="s">
+        <v>198</v>
+      </c>
+      <c r="G16" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="E17" t="s">
+        <v>202</v>
+      </c>
+      <c r="G17" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
+      <c r="A19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" s="12"/>
+      <c r="D20" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="T21" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
+      <c r="A25" s="12"/>
+      <c r="D25" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
+      <c r="D26" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
+      <c r="D27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
+      <c r="D28" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="A30" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
+      <c r="D32" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="D33" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="D34" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="D35" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="D36" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="D37" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="D38" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="D40" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="12"/>
+      <c r="D41" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="D42" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="D43" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="D44" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="D45" s="7"/>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="D48" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
+      <c r="A49" s="12"/>
+      <c r="D49" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19">
+      <c r="A50" s="12"/>
+      <c r="D50" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19">
+      <c r="D51" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19">
+      <c r="D53" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19">
+      <c r="D54" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19">
+      <c r="B56" s="12"/>
+      <c r="D56" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19">
+      <c r="B57" s="12"/>
+      <c r="D57" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19">
+      <c r="E58" t="s">
+        <v>236</v>
+      </c>
+      <c r="R58" t="s">
+        <v>235</v>
+      </c>
+      <c r="S58" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="12"/>
+      <c r="D65" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="12"/>
+      <c r="D69" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="D70" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="12"/>
+      <c r="D72" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="D73" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="D74" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="D75" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="D76" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="D77" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="12"/>
+      <c r="D79" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="D83" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="E84" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="E85" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="E86" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="E87" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="E88" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="E89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="E90" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="D92" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="12"/>
+      <c r="D93" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="12"/>
+      <c r="D94" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="D95" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="D99" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="D103" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="D104" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="D105" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8813AF9C-3F6B-4300-BAE0-5E95D2DD0CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FB52D4-3E05-40EA-969D-813892DB504E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="266">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -1308,6 +1308,96 @@
   <si>
     <t>”がない</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進捗更新エージェント</t>
+    <rPh sb="0" eb="4">
+      <t>シンチョクコウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  --role-name AmazonBedrockAgentCoreSDKRuntime-ap-northeast-1-b93c04ec99 `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --policy-document file://task-agent/dynamodb-access-policy-clients.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --policy-name task-agent-dynamodb-clients `</t>
+  </si>
+  <si>
+    <t>cd task-agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy-Item ..\layer\python\task_repository.py . -Force </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>agentcore launch `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --env TASKS_TABLE=Tasks `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --env CLIENTS_TABLE=TaskClients `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --env SERIES_TABLE=TaskSeries `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --env FRAMES_TABLE=TaskFrames `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --env HISTORY_TABLE=TaskHistory `</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --env AGENT_JOBS_TABLE=TaskAgentJobs</t>
+  </si>
+  <si>
+    <t>task-agent\.claude\skills\progress-update\SKILL.md</t>
+  </si>
+  <si>
+    <t>スキル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>  担当者・ステータスが未入力のレコードが溜まることがある(HistoryPanel.jsxの</t>
+  </si>
+  <si>
+    <t>  「CSVアップロード」機能は各行をcontentへそのまま取り込み、他の項目は空で登録する</t>
+  </si>
+  <si>
+    <t>  ため)。このスキルはそうした履歴レコードを順に読み取り、contentの内容を解釈して</t>
+  </si>
+  <si>
+    <t>  日付・分類・担当者・ステータスを判定・更新する。</t>
+  </si>
+  <si>
+    <t>  「進捗を更新して」「履歴を整理して」「MMの進捗を更新して」「履歴のステータスを</t>
+  </si>
+  <si>
+    <t>  埋めて」のように言われたら必ずこのスキルを使うこと。使用時は最初に必ずどの関与先</t>
+  </si>
+  <si>
+    <t>  (案件コード)を処理するか確認してから、mcp__task-manager__list_history で該当関与先</t>
+  </si>
+  <si>
+    <t>  の履歴を取得すること。領収書のOCR・リネームは行わない(それは receipt-ocr-filelist</t>
+  </si>
+  <si>
+    <t>  スキルの役割)。</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>name: progress-update</t>
+  </si>
+  <si>
+    <t>description: |</t>
+  </si>
+  <si>
+    <t>  taskmanagerの履歴(TaskHistory)には、内容(content)欄だけが埋まっていて日付・分類・</t>
   </si>
 </sst>
 </file>
@@ -1420,7 +1510,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1445,6 +1535,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1459,7 +1555,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1482,6 +1578,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -2994,7 +3091,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89218E65-9CD0-49A4-A7F2-71B0476A86F1}">
-  <dimension ref="A1:T105"/>
+  <dimension ref="A1:T139"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="3" width="2.5625" customWidth="1"/>
@@ -3385,6 +3482,7 @@
       </c>
     </row>
     <row r="99" spans="1:4">
+      <c r="A99" s="12"/>
       <c r="D99" t="s">
         <v>189</v>
       </c>
@@ -3395,18 +3493,167 @@
       </c>
     </row>
     <row r="103" spans="1:4">
+      <c r="A103" s="14"/>
       <c r="D103" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="104" spans="1:4">
+      <c r="A104" s="14"/>
       <c r="D104" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="105" spans="1:4">
+      <c r="A105" s="14"/>
       <c r="D105" t="s">
         <v>192</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" s="9" customFormat="1"/>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="D110" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="D111" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="D112" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="D113" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="D115" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="D116" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="D118" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="D119" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4">
+      <c r="D120" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="D121" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="D122" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="D123" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="D124" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4">
+      <c r="B125" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="C126" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="D127" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="D128" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="129" spans="4:4">
+      <c r="D129" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="130" spans="4:4">
+      <c r="D130" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="131" spans="4:4">
+      <c r="D131" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="132" spans="4:4">
+      <c r="D132" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="133" spans="4:4">
+      <c r="D133" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="134" spans="4:4">
+      <c r="D134" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="135" spans="4:4">
+      <c r="D135" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="136" spans="4:4">
+      <c r="D136" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="137" spans="4:4">
+      <c r="D137" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="138" spans="4:4">
+      <c r="D138" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="139" spans="4:4">
+      <c r="D139" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FB52D4-3E05-40EA-969D-813892DB504E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A583DD71-FE6E-45D9-8865-FBA70E2DED9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体図" sheetId="2" r:id="rId1"/>
@@ -2633,7 +2633,7 @@
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="3" t="s">
         <v>34</v>
       </c>
     </row>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A583DD71-FE6E-45D9-8865-FBA70E2DED9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F220F0DC-340A-4A96-BF1F-AC3092637FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="267">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -1398,6 +1398,10 @@
   </si>
   <si>
     <t>  taskmanagerの履歴(TaskHistory)には、内容(content)欄だけが埋まっていて日付・分類・</t>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -2363,7 +2367,9 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="10"/>
+      <c r="A24" s="10" t="s">
+        <v>266</v>
+      </c>
       <c r="C24" s="2" t="s">
         <v>2</v>
       </c>
@@ -2616,13 +2622,17 @@
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="10"/>
+      <c r="A75" s="10" t="s">
+        <v>266</v>
+      </c>
       <c r="D75" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="10"/>
+      <c r="A76" s="10" t="s">
+        <v>266</v>
+      </c>
       <c r="D76" s="2" t="s">
         <v>131</v>
       </c>
@@ -2638,7 +2648,9 @@
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="10"/>
+      <c r="A79" s="10" t="s">
+        <v>266</v>
+      </c>
       <c r="D79" s="2" t="s">
         <v>134</v>
       </c>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F220F0DC-340A-4A96-BF1F-AC3092637FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C4B652-E42C-4339-9FDA-804FDAAE2A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C4B652-E42C-4339-9FDA-804FDAAE2A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9B7063-D8BB-4FA7-947F-2B2B8EDD0853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体図" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="273">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -1401,6 +1401,37 @@
   </si>
   <si>
     <t>x</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>deploy手順（更新）</t>
+    <rPh sb="6" eb="8">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>共有モジュールコピー</t>
+  </si>
+  <si>
+    <t>デプロイ実行</t>
+  </si>
+  <si>
+    <t>cd task-agent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択肢はdefault</t>
+    <rPh sb="0" eb="3">
+      <t>センタクシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>agentcore launch --env TASKS_TABLE=Tasks --env CLIENTS_TABLE=TaskClients --env SERIES_TABLE=TaskSeries --env FRAMES_TABLE=TaskFrames --env HISTORY_TABLE=TaskHistory --env AGENT_JOBS_TABLE=TaskAgentJobs --env CLASSIFICATION_RULES_TABLE=TaskClassificationRules</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1559,7 +1590,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1583,6 +1614,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -3103,7 +3135,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89218E65-9CD0-49A4-A7F2-71B0476A86F1}">
-  <dimension ref="A1:T139"/>
+  <dimension ref="A1:T150"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="3" width="2.5625" customWidth="1"/>
@@ -3613,59 +3645,105 @@
         <v>264</v>
       </c>
     </row>
-    <row r="129" spans="4:4">
+    <row r="129" spans="1:4">
       <c r="D129" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="130" spans="4:4">
+    <row r="130" spans="1:4">
       <c r="D130" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="131" spans="4:4">
+    <row r="131" spans="1:4">
       <c r="D131" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="132" spans="4:4">
+    <row r="132" spans="1:4">
       <c r="D132" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="133" spans="4:4">
+    <row r="133" spans="1:4">
       <c r="D133" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="134" spans="4:4">
+    <row r="134" spans="1:4">
       <c r="D134" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="135" spans="4:4">
+    <row r="135" spans="1:4">
       <c r="D135" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="136" spans="4:4">
+    <row r="136" spans="1:4">
       <c r="D136" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="137" spans="4:4">
+    <row r="137" spans="1:4">
       <c r="D137" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="138" spans="4:4">
+    <row r="138" spans="1:4">
       <c r="D138" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="139" spans="4:4">
+    <row r="139" spans="1:4">
       <c r="D139" t="s">
         <v>262</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" s="9" customFormat="1">
+      <c r="A141" s="9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" s="15" customFormat="1">
+      <c r="D142" s="15" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="B143" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="10"/>
+      <c r="D144" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="B146" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="10"/>
+      <c r="D147" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="E148" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="D149" s="7"/>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="10"/>
+      <c r="D150" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9B7063-D8BB-4FA7-947F-2B2B8EDD0853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1925B6B9-9454-4FC9-9399-5D87D818C919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1590,7 +1590,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1614,7 +1614,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -3705,8 +3704,8 @@
         <v>267</v>
       </c>
     </row>
-    <row r="142" spans="1:4" s="15" customFormat="1">
-      <c r="D142" s="15" t="s">
+    <row r="142" spans="1:4">
+      <c r="D142" t="s">
         <v>270</v>
       </c>
     </row>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1925B6B9-9454-4FC9-9399-5D87D818C919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695C370B-3AC8-4008-A7FF-365A2C7F9A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="277">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -1432,6 +1432,22 @@
   </si>
   <si>
     <t>agentcore launch --env TASKS_TABLE=Tasks --env CLIENTS_TABLE=TaskClients --env SERIES_TABLE=TaskSeries --env FRAMES_TABLE=TaskFrames --env HISTORY_TABLE=TaskHistory --env AGENT_JOBS_TABLE=TaskAgentJobs --env CLASSIFICATION_RULES_TABLE=TaskClassificationRules</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aws iam put-role-policy \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --role-name AmazonBedrockAgentCoreSDKRuntime-ap-northeast-1-b93c04ec99 \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  --policy-name &lt;上で確認したポリシー名&gt; \</t>
+  </si>
+  <si>
+    <t>権限問題</t>
+    <rPh sb="0" eb="4">
+      <t>ケンゲンモンダイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3134,7 +3150,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89218E65-9CD0-49A4-A7F2-71B0476A86F1}">
-  <dimension ref="A1:T150"/>
+  <dimension ref="A1:T164"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="3" width="2.5625" customWidth="1"/>
@@ -3745,6 +3761,32 @@
         <v>272</v>
       </c>
     </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="12"/>
+      <c r="B156" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="161" spans="4:4">
+      <c r="D161" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="162" spans="4:4">
+      <c r="D162" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="163" spans="4:4">
+      <c r="D163" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="164" spans="4:4">
+      <c r="D164" t="s">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695C370B-3AC8-4008-A7FF-365A2C7F9A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2133F30-C52E-4142-92E8-5BE63351A962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体図" sheetId="2" r:id="rId1"/>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2133F30-C52E-4142-92E8-5BE63351A962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421ABFA7-04AC-460D-8F95-5D3E39FB41EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="297">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -883,16 +883,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>以下旧情報</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="2" eb="5">
-      <t>キュウジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>task managerに統合一元化　（taskmanager, task-mcp-server, agentmanager)</t>
     <rPh sb="13" eb="15">
       <t>トウゴウ</t>
@@ -1450,12 +1440,142 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>(Amorphous Console)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>更新Deploy手順</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下　新規作成時手順メモ</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>サクセイジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(MCP)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(現在はapi_src/app.py)</t>
+    <rPh sb="1" eb="3">
+      <t>ゲンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(現在はmcp_src/app.py)</t>
+    <rPh sb="1" eb="3">
+      <t>ゲンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新規開発時手順メモ</t>
+    <rPh sb="0" eb="5">
+      <t>シンキカイハツジ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GoogleDriveアクセス用トークン更新</t>
+    <rPh sb="15" eb="16">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026.8.10修正</t>
+    <rPh sb="9" eb="11">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>client secretが変わってしまっていたため修正</t>
+    <rPh sb="14" eb="15">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クライアントID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1011354473098-od5n1po1v94lfv87qesep52i11rht3m3.apps.googleusercontent.com</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クライアントシークレット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>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</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>=== Obtained token (store this in Secrets Manager) ===</t>
+  </si>
+  <si>
+    <t>========================================================</t>
+  </si>
+  <si>
+    <t>{"refresh_token": "1//0eK8JH9loAwrECgYIARAAGA4SNwF-L9Irla3t_05ETaJbKs1awTft6EwDZbeqIo4-eTSSnzmrh0yHupPgi8hqria5_Pc7oCdxTZo", "client_id": "1011354473098-od5n1po1v94lfv87qesep52i11rht3m3.apps.googleusercontent.com", "client_secret": "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", "token_uri": "https://oauth2.googleapis.com/token", "scopes": ["https://www.googleapis.com/auth/drive"]}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aws secretsmanager put-secret-value --region ap-northeast-1 --secret-id task-agent/google-drive-user-token --secret-string '{"refresh_token": "1//0eK8JH9loAwrECgYIARAAGA4SNwF-L9Irla3t_05ETaJbKs1awTft6EwDZbeqIo4-eTSSnzmrh0yHupPgi8hqria5_Pc7oCdxTZo", "client_id": "1011354473098-od5n1po1v94lfv87qesep52i11rht3m3.apps.googleusercontent.com", "client_secret": "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", "token_uri": "https://oauth2.googleapis.com/token", "scopes": ["https://www.googleapis.com/auth/drive"]}'</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tmp-token.jsonを作成</t>
+    <rPh sb="15" eb="17">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1560,8 +1680,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1592,6 +1719,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1606,7 +1739,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1630,6 +1763,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1659,14 +1794,14 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>19051</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>476330</xdr:colOff>
-      <xdr:row>138</xdr:row>
-      <xdr:rowOff>188077</xdr:rowOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>188078</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1708,13 +1843,13 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>585788</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>200026</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>257240</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>57584</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1752,14 +1887,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>33338</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>33338</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>223229</xdr:rowOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>223230</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1796,14 +1931,14 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>52387</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>52389</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>643017</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>190352</xdr:rowOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>190353</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1828,6 +1963,182 @@
         <a:xfrm>
           <a:off x="10239375" y="13034964"/>
           <a:ext cx="8820230" cy="809476"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4762</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>61913</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>319087</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>51288</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEC4529A-6B2F-AE9B-DB60-F58C68EF8275}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1962150" y="19321463"/>
+          <a:ext cx="5800725" cy="1332400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>52387</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>219523</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>23847</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>5776</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D979BAF6-886D-0DD2-C3D9-B3FB512643DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5438775" y="4024761"/>
+          <a:ext cx="2714660" cy="457766"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>391327</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>4763</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>214367</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DC7AC62-90D1-768D-766A-15DBB767313D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21551115" y="3810001"/>
+          <a:ext cx="5995240" cy="347662"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>42863</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>52388</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>323589</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{088D64BC-4B5F-8861-15FD-7373A372CABB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10915651" y="3857626"/>
+          <a:ext cx="10567726" cy="323850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2283,7 +2594,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M184"/>
+  <dimension ref="A1:M193"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="2" width="2.5625" customWidth="1"/>
@@ -2293,46 +2604,54 @@
       <c r="A1" t="s">
         <v>4</v>
       </c>
+      <c r="D1" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="B3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="C4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" t="s">
         <v>149</v>
-      </c>
-      <c r="E4" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="C5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="C6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
       </c>
       <c r="J6" t="s">
-        <v>154</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2342,24 +2661,33 @@
       </c>
     </row>
     <row r="10" spans="1:10">
+      <c r="A10" s="10" t="s">
+        <v>265</v>
+      </c>
       <c r="C10" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" t="s">
         <v>155</v>
       </c>
-      <c r="D11" t="s">
-        <v>156</v>
-      </c>
     </row>
     <row r="12" spans="1:10">
+      <c r="A12" s="10" t="s">
+        <v>265</v>
+      </c>
       <c r="C12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
+      <c r="A13" s="10" t="s">
+        <v>265</v>
+      </c>
       <c r="C13" s="2" t="s">
         <v>131</v>
       </c>
@@ -2370,778 +2698,833 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
+      <c r="A16" s="10" t="s">
+        <v>265</v>
+      </c>
       <c r="C16" s="2" t="s">
         <v>134</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="B17" t="s">
-        <v>157</v>
+      <c r="B17" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="C17" s="2"/>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5">
+      <c r="A18" s="10" t="s">
+        <v>265</v>
+      </c>
       <c r="C18" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" s="9" customFormat="1">
-      <c r="A20" s="11" t="s">
+      <c r="C19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="C20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="C21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="C22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="C23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="C24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="C25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="C26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="C27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="9" customFormat="1">
+      <c r="A29" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="B21" t="s">
+    <row r="30" spans="1:5">
+      <c r="B30" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="C22" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="B25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="C26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" s="9" customFormat="1">
-      <c r="A27" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="C28" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="D29" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="D30" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="C31" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" s="9" customFormat="1">
+      <c r="A36" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="C37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="D38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="C40" t="s">
         <v>8</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E40" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="D32" s="3" t="s">
+    <row r="41" spans="1:6">
+      <c r="D41" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
-      <c r="D33" s="3" t="s">
+    <row r="42" spans="1:6">
+      <c r="D42" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
-      <c r="C35" t="s">
+    <row r="44" spans="1:6">
+      <c r="C44" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="D36" t="s">
+    <row r="45" spans="1:6">
+      <c r="D45" t="s">
         <v>10</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F45" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="2:6">
-      <c r="D37" t="s">
+    <row r="46" spans="1:6">
+      <c r="D46" t="s">
         <v>13</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F46" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
-      <c r="D38" s="1" t="s">
+    <row r="47" spans="1:6">
+      <c r="D47" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F47" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="D39" t="s">
+    <row r="48" spans="1:6">
+      <c r="D48" t="s">
         <v>16</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F48" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
-      <c r="D40" t="s">
+    <row r="49" spans="2:6">
+      <c r="D49" t="s">
         <v>17</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F49" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="2:6">
-      <c r="D41" t="s">
+    <row r="50" spans="2:6">
+      <c r="D50" t="s">
         <v>19</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F50" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="2:6">
-      <c r="D42" t="s">
+    <row r="51" spans="2:6">
+      <c r="D51" t="s">
         <v>20</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F51" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
-      <c r="D43" t="s">
+    <row r="52" spans="2:6">
+      <c r="D52" t="s">
         <v>22</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F52" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="2:6">
-      <c r="B45" t="s">
+    <row r="54" spans="2:6">
+      <c r="B54" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
-      <c r="D46" t="s">
+    <row r="55" spans="2:6">
+      <c r="D55" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="47" spans="2:6">
-      <c r="D47" t="s">
+    <row r="56" spans="2:6">
+      <c r="D56" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="2:4">
-      <c r="C49" t="s">
+    <row r="58" spans="2:6">
+      <c r="C58" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="2:4">
-      <c r="C50" t="s">
+    <row r="59" spans="2:6">
+      <c r="C59" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="2:4">
-      <c r="B52" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="2:4">
-      <c r="C53" t="s">
+    <row r="62" spans="2:6">
+      <c r="C62" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="2:4">
-      <c r="D54" t="s">
+    <row r="63" spans="2:6">
+      <c r="D63" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="2:4">
-      <c r="D55" t="s">
+    <row r="64" spans="2:6">
+      <c r="D64" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4">
-      <c r="D56" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4">
-      <c r="D57" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4">
-      <c r="D58" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4">
-      <c r="D59" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4">
-      <c r="D60" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4">
-      <c r="D61" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4">
-      <c r="D62" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4">
-      <c r="D63" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4">
-      <c r="D64" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="D65" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="D66" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="D67" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="D68" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="D69" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" t="s">
-        <v>35</v>
+      <c r="D70" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="C71" t="s">
-        <v>33</v>
+      <c r="D71" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="D72" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="D73" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="D74" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="D75" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="D76" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="C80" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="D81" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="D82" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
-      <c r="C74" t="s">
+    <row r="83" spans="1:5">
+      <c r="C83" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="D75" s="2" t="s">
+    <row r="84" spans="1:5">
+      <c r="A84" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="D76" s="2" t="s">
+    <row r="85" spans="1:5">
+      <c r="A85" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
-      <c r="D77" t="s">
+    <row r="86" spans="1:5">
+      <c r="D86" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
-      <c r="D78" s="3" t="s">
+    <row r="87" spans="1:5">
+      <c r="D87" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="D79" s="2" t="s">
+    <row r="88" spans="1:5">
+      <c r="A88" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="21.75">
-      <c r="C81" s="4" t="s">
+    <row r="90" spans="1:5" ht="21.75">
+      <c r="C90" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="82" spans="1:13">
-      <c r="C82" t="s">
+    <row r="91" spans="1:5">
+      <c r="C91" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
-      <c r="C83" s="5" t="s">
+    <row r="92" spans="1:5">
+      <c r="C92" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="84" spans="1:13">
-      <c r="C84" s="6" t="s">
+    <row r="93" spans="1:5">
+      <c r="C93" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="85" spans="1:13">
-      <c r="C85" s="6" t="s">
+    <row r="94" spans="1:5">
+      <c r="C94" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
-      <c r="C86" s="5" t="s">
+    <row r="95" spans="1:5">
+      <c r="C95" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E86" s="7" t="s">
+      <c r="E95" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="87" spans="1:13">
-      <c r="C87" s="5" t="s">
+    <row r="96" spans="1:5">
+      <c r="C96" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E87" s="8" t="s">
+      <c r="E96" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="88" spans="1:13">
-      <c r="C88" s="5" t="s">
+    <row r="97" spans="1:13">
+      <c r="C97" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="89" spans="1:13">
-      <c r="C89" s="6" t="s">
+    <row r="98" spans="1:13">
+      <c r="C98" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="91" spans="1:13" s="9" customFormat="1">
-      <c r="A91" s="9" t="s">
+    <row r="100" spans="1:13" s="9" customFormat="1">
+      <c r="A100" s="9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="92" spans="1:13">
-      <c r="B92" t="s">
+    <row r="101" spans="1:13">
+      <c r="B101" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="93" spans="1:13">
-      <c r="B93" t="s">
+      <c r="F101" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13">
+      <c r="B102" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="94" spans="1:13">
-      <c r="B94" t="s">
+    <row r="103" spans="1:13">
+      <c r="B103" t="s">
         <v>65</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E103" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="96" spans="1:13">
-      <c r="C96" t="s">
+    <row r="105" spans="1:13">
+      <c r="C105" t="s">
         <v>36</v>
       </c>
-      <c r="M96" t="s">
+      <c r="M105" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="97" spans="3:13">
-      <c r="D97" s="2" t="s">
+    <row r="106" spans="1:13">
+      <c r="D106" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M97" t="s">
+      <c r="M106" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="98" spans="3:13">
-      <c r="D98" t="s">
+    <row r="107" spans="1:13">
+      <c r="D107" t="s">
         <v>26</v>
       </c>
-      <c r="M98" t="s">
+      <c r="M107" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="99" spans="3:13">
-      <c r="D99" t="s">
+    <row r="108" spans="1:13">
+      <c r="D108" t="s">
         <v>52</v>
       </c>
-      <c r="M99" t="s">
+      <c r="M108" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="100" spans="3:13">
-      <c r="D100" t="s">
+    <row r="109" spans="1:13">
+      <c r="D109" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="101" spans="3:13">
-      <c r="E101" t="s">
+    <row r="110" spans="1:13">
+      <c r="E110" t="s">
         <v>10</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G110" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="3:13">
-      <c r="E102" t="s">
+    <row r="111" spans="1:13">
+      <c r="E111" t="s">
         <v>13</v>
       </c>
-      <c r="G102" t="s">
+      <c r="G111" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="3:13">
-      <c r="E103" s="1" t="s">
+    <row r="112" spans="1:13">
+      <c r="E112" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G103" t="s">
+      <c r="G112" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="3:13">
-      <c r="E104" t="s">
+    <row r="113" spans="3:8">
+      <c r="E113" t="s">
         <v>16</v>
       </c>
-      <c r="G104" t="s">
+      <c r="G113" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="105" spans="3:13">
-      <c r="E105" t="s">
+    <row r="114" spans="3:8">
+      <c r="E114" t="s">
         <v>17</v>
       </c>
-      <c r="G105" t="s">
+      <c r="G114" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="3:13">
-      <c r="E106" t="s">
+    <row r="115" spans="3:8">
+      <c r="E115" t="s">
         <v>19</v>
       </c>
-      <c r="G106" t="s">
+      <c r="G115" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="107" spans="3:13">
-      <c r="E107" t="s">
+    <row r="116" spans="3:8">
+      <c r="E116" t="s">
         <v>20</v>
       </c>
-      <c r="G107" t="s">
+      <c r="G116" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="3:13">
-      <c r="E108" t="s">
+    <row r="117" spans="3:8">
+      <c r="E117" t="s">
         <v>22</v>
       </c>
-      <c r="G108" t="s">
+      <c r="G117" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="109" spans="3:13">
-      <c r="E109" t="s">
+    <row r="118" spans="3:8">
+      <c r="E118" t="s">
         <v>68</v>
       </c>
-      <c r="H109" t="s">
+      <c r="H118" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="110" spans="3:13">
-      <c r="C110" t="s">
+    <row r="119" spans="3:8">
+      <c r="C119" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="111" spans="3:13">
-      <c r="D111" t="s">
+    <row r="120" spans="3:8">
+      <c r="D120" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="112" spans="3:13">
-      <c r="D112" t="s">
+    <row r="121" spans="3:8">
+      <c r="D121" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
-      <c r="D113" t="s">
+    <row r="122" spans="3:8">
+      <c r="D122" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
-      <c r="D114" t="s">
+    <row r="123" spans="3:8">
+      <c r="D123" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="120" spans="1:5" s="9" customFormat="1">
-      <c r="A120" s="9" t="s">
+    <row r="129" spans="1:5" s="9" customFormat="1">
+      <c r="A129" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E120" s="9" t="s">
+      <c r="E129" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
-      <c r="D121" t="s">
+    <row r="130" spans="1:5">
+      <c r="D130" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
-      <c r="E122" t="s">
+    <row r="131" spans="1:5">
+      <c r="E131" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
-      <c r="E123" t="s">
+    <row r="132" spans="1:5">
+      <c r="E132" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
-      <c r="E124" t="s">
+    <row r="133" spans="1:5">
+      <c r="E133" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
-      <c r="E125" t="s">
+    <row r="134" spans="1:5">
+      <c r="E134" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
-      <c r="E126" t="s">
+    <row r="135" spans="1:5">
+      <c r="E135" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
-      <c r="E127" t="s">
+    <row r="136" spans="1:5">
+      <c r="E136" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
-      <c r="E128" t="s">
+    <row r="137" spans="1:5">
+      <c r="E137" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="130" spans="5:5">
-      <c r="E130" t="s">
+    <row r="139" spans="1:5">
+      <c r="E139" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="131" spans="5:5">
-      <c r="E131" t="s">
+    <row r="140" spans="1:5">
+      <c r="E140" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="132" spans="5:5">
-      <c r="E132" t="s">
+    <row r="141" spans="1:5">
+      <c r="E141" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="133" spans="5:5">
-      <c r="E133" t="s">
+    <row r="142" spans="1:5">
+      <c r="E142" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="134" spans="5:5">
-      <c r="E134" t="s">
+    <row r="143" spans="1:5">
+      <c r="E143" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="142" spans="5:5">
-      <c r="E142" t="s">
+    <row r="151" spans="5:5">
+      <c r="E151" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="143" spans="5:5">
-      <c r="E143" t="s">
+    <row r="152" spans="5:5">
+      <c r="E152" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="144" spans="5:5">
-      <c r="E144" t="s">
+    <row r="153" spans="5:5">
+      <c r="E153" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="145" spans="4:5">
-      <c r="E145" t="s">
+    <row r="154" spans="5:5">
+      <c r="E154" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="146" spans="4:5">
-      <c r="E146" t="s">
+    <row r="155" spans="5:5">
+      <c r="E155" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="148" spans="4:5">
-      <c r="E148" t="s">
+    <row r="157" spans="5:5">
+      <c r="E157" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="149" spans="4:5">
-      <c r="E149" t="s">
+    <row r="158" spans="5:5">
+      <c r="E158" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="150" spans="4:5">
-      <c r="E150" t="s">
+    <row r="159" spans="5:5">
+      <c r="E159" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="151" spans="4:5">
-      <c r="E151" t="s">
+    <row r="160" spans="5:5">
+      <c r="E160" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="152" spans="4:5">
-      <c r="E152" t="s">
+    <row r="161" spans="4:5">
+      <c r="E161" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="153" spans="4:5">
-      <c r="E153" t="s">
+    <row r="162" spans="4:5">
+      <c r="E162" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="155" spans="4:5">
-      <c r="E155" t="s">
+    <row r="164" spans="4:5">
+      <c r="E164" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="156" spans="4:5">
-      <c r="E156" t="s">
+    <row r="165" spans="4:5">
+      <c r="E165" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="158" spans="4:5">
-      <c r="D158" t="s">
+    <row r="167" spans="4:5">
+      <c r="D167" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="159" spans="4:5">
-      <c r="E159" t="s">
+    <row r="168" spans="4:5">
+      <c r="E168" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="160" spans="4:5">
-      <c r="E160" t="s">
+    <row r="169" spans="4:5">
+      <c r="E169" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
-      <c r="E161" t="s">
+    <row r="170" spans="4:5">
+      <c r="E170" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
-      <c r="E162" t="s">
+    <row r="171" spans="4:5">
+      <c r="E171" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
-      <c r="E164" t="s">
+    <row r="173" spans="4:5">
+      <c r="E173" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
-      <c r="E166" t="s">
+    <row r="175" spans="4:5">
+      <c r="E175" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
-      <c r="E167" t="s">
+    <row r="176" spans="4:5">
+      <c r="E176" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="169" spans="1:5" s="9" customFormat="1">
-      <c r="A169" s="11" t="s">
+    <row r="178" spans="1:5" s="9" customFormat="1">
+      <c r="A178" s="11" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
-      <c r="C171" t="s">
+    <row r="180" spans="1:5">
+      <c r="C180" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
-      <c r="E172" t="s">
+    <row r="181" spans="1:5">
+      <c r="E181" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
-      <c r="E173" t="s">
+    <row r="182" spans="1:5">
+      <c r="E182" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
-      <c r="E174" t="s">
+    <row r="183" spans="1:5">
+      <c r="E183" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
-      <c r="C176" t="s">
+    <row r="185" spans="1:5">
+      <c r="C185" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
-      <c r="A178" s="10"/>
-      <c r="C178" t="s">
+    <row r="187" spans="1:5">
+      <c r="A187" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C187" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
-      <c r="A180" s="10"/>
-      <c r="C180" t="s">
+    <row r="189" spans="1:5">
+      <c r="A189" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C189" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
-      <c r="A184" t="s">
+    <row r="193" spans="1:3">
+      <c r="A193" t="s">
         <v>107</v>
       </c>
-      <c r="C184" t="s">
+      <c r="C193" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="E87" r:id="rId1" xr:uid="{6779DE2A-DCC0-4F58-8418-AF9B609FD587}"/>
+    <hyperlink ref="E96" r:id="rId1" xr:uid="{6779DE2A-DCC0-4F58-8418-AF9B609FD587}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
@@ -3150,641 +3533,728 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89218E65-9CD0-49A4-A7F2-71B0476A86F1}">
-  <dimension ref="A1:T164"/>
+  <dimension ref="A1:T186"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="3" width="2.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="B2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="D4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="9" customFormat="1">
+      <c r="A2" s="9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="D3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="B4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="10"/>
       <c r="D5" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+    <row r="7" spans="1:19">
+      <c r="B7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="D8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="12"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="10"/>
       <c r="D9" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
+    <row r="10" spans="1:19">
+      <c r="E10" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" s="10"/>
+      <c r="D12" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="B14" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" s="10"/>
+      <c r="D15" t="s">
+        <v>233</v>
+      </c>
+      <c r="S15" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="D16" t="s">
+        <v>231</v>
+      </c>
+      <c r="S16" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="S17" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="B18" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="D18" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" s="10"/>
+      <c r="D20" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="10"/>
+      <c r="B22" t="s">
+        <v>296</v>
+      </c>
+      <c r="D22" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="18" customHeight="1"/>
+    <row r="24" spans="1:19" s="9" customFormat="1" ht="18" customHeight="1">
+      <c r="A24" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="B25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="D27" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="D28" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="D31" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" s="12"/>
+      <c r="D32" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="A34" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
+      <c r="D35" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
+      <c r="A36" s="12"/>
+      <c r="D36" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
+      <c r="A37" s="12"/>
+      <c r="D37" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="D12" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="12"/>
-      <c r="D13" t="s">
+    <row r="38" spans="1:20">
+      <c r="E38" t="s">
+        <v>199</v>
+      </c>
+      <c r="G38" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
+      <c r="E39" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="12"/>
-      <c r="D14" t="s">
+      <c r="G39" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
+      <c r="E40" t="s">
+        <v>201</v>
+      </c>
+      <c r="G40" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
+      <c r="A42" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="E15" t="s">
-        <v>200</v>
-      </c>
-      <c r="G15" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="E16" t="s">
-        <v>198</v>
-      </c>
-      <c r="G16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="E17" t="s">
+    <row r="43" spans="1:20">
+      <c r="A43" s="12"/>
+      <c r="D43" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
+      <c r="T44" t="s">
         <v>202</v>
       </c>
-      <c r="G17" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" t="s">
+    </row>
+    <row r="48" spans="1:20">
+      <c r="A48" s="12"/>
+      <c r="D48" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="12"/>
-      <c r="D20" t="s">
+    <row r="49" spans="1:4">
+      <c r="D49" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
-      <c r="T21" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="12"/>
-      <c r="D25" t="s">
+    <row r="50" spans="1:4">
+      <c r="D50" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
-      <c r="D26" t="s">
+    <row r="51" spans="1:4">
+      <c r="D51" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="D55" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="D56" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="D57" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="D58" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="D59" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="D60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="D61" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="D63" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="12"/>
+      <c r="D64" s="7" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
-      <c r="D27" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="D28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
-      <c r="D32" t="s">
+    <row r="65" spans="1:4">
+      <c r="D65" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="D66" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="D67" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="D68" s="7"/>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
-      <c r="D33" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="D34" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="D35" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="D36" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="D37" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="D38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="D40" s="13" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="12"/>
-      <c r="D41" s="7" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="D42" s="13" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="D43" s="13" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="D44" s="13" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="D45" s="7"/>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
+    <row r="71" spans="1:4">
+      <c r="D71" t="s">
         <v>177</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="D48" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19">
-      <c r="A49" s="12"/>
-      <c r="D49" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19">
-      <c r="A50" s="12"/>
-      <c r="D50" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19">
-      <c r="D51" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19">
-      <c r="D53" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19">
-      <c r="D54" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19">
-      <c r="B56" s="12"/>
-      <c r="D56" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19">
-      <c r="B57" s="12"/>
-      <c r="D57" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19">
-      <c r="E58" t="s">
-        <v>236</v>
-      </c>
-      <c r="R58" t="s">
-        <v>235</v>
-      </c>
-      <c r="S58" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="12"/>
-      <c r="D65" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="12"/>
-      <c r="D69" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="D70" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="12"/>
       <c r="D72" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
     </row>
     <row r="73" spans="1:4">
+      <c r="A73" s="12"/>
       <c r="D73" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="D74" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="D75" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="D76" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="D77" t="s">
-        <v>182</v>
+        <v>231</v>
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="12"/>
+      <c r="B79" s="12"/>
       <c r="D79" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="D83" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="E84" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="E85" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="E86" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="E87" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="B80" s="12"/>
+      <c r="D80" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="81" spans="4:19">
+      <c r="E81" t="s">
+        <v>235</v>
+      </c>
+      <c r="R81" t="s">
+        <v>234</v>
+      </c>
+      <c r="S81" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="87" spans="4:19">
+      <c r="D87" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="88" spans="4:19">
       <c r="E88" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="89" spans="4:19">
       <c r="E89" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>286</v>
+      </c>
+      <c r="G89" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="90" spans="4:19">
       <c r="E90" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="D92" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="12"/>
-      <c r="D93" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="12"/>
-      <c r="D94" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="D95" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="12"/>
-      <c r="D99" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" t="s">
-        <v>186</v>
+        <v>288</v>
+      </c>
+      <c r="G90" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="12"/>
+      <c r="D98" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="12"/>
+      <c r="D102" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="14"/>
       <c r="D103" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="14"/>
-      <c r="D104" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="14"/>
+      <c r="A105" s="12"/>
       <c r="D105" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" s="9" customFormat="1"/>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="D106" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="D107" t="s">
+        <v>216</v>
+      </c>
+    </row>
     <row r="108" spans="1:4">
-      <c r="A108" t="s">
-        <v>238</v>
+      <c r="D108" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="D109" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="D110" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="D111" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="12"/>
+      <c r="D112" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="D116" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="E117" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="E118" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="E119" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="E120" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="E121" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="E122" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="E123" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="D125" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="12"/>
+      <c r="D126" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="12"/>
+      <c r="D127" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="D128" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="12"/>
+      <c r="D132" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="14"/>
+      <c r="D136" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="14"/>
+      <c r="D137" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="14"/>
+      <c r="D138" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" s="9" customFormat="1"/>
+    <row r="141" spans="1:4">
+      <c r="A141" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="D143" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="D144" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="D145" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="D146" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
-      <c r="D112" t="s">
+    <row r="148" spans="2:4">
+      <c r="D148" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="113" spans="2:4">
-      <c r="D113" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4">
-      <c r="D115" t="s">
+    <row r="149" spans="2:4">
+      <c r="D149" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="116" spans="2:4">
-      <c r="D116" t="s">
+    <row r="151" spans="2:4">
+      <c r="D151" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="118" spans="2:4">
-      <c r="D118" t="s">
+    <row r="152" spans="2:4">
+      <c r="D152" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="119" spans="2:4">
-      <c r="D119" t="s">
+    <row r="153" spans="2:4">
+      <c r="D153" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="120" spans="2:4">
-      <c r="D120" t="s">
+    <row r="154" spans="2:4">
+      <c r="D154" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="121" spans="2:4">
-      <c r="D121" t="s">
+    <row r="155" spans="2:4">
+      <c r="D155" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="122" spans="2:4">
-      <c r="D122" t="s">
+    <row r="156" spans="2:4">
+      <c r="D156" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="123" spans="2:4">
-      <c r="D123" t="s">
+    <row r="157" spans="2:4">
+      <c r="D157" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="124" spans="2:4">
-      <c r="D124" t="s">
+    <row r="158" spans="2:4">
+      <c r="B158" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="C159" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="125" spans="2:4">
-      <c r="B125" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="126" spans="2:4">
-      <c r="C126" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="127" spans="2:4">
-      <c r="D127" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="128" spans="2:4">
-      <c r="D128" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
-      <c r="D129" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="D130" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4">
-      <c r="D131" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
-      <c r="D132" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
-      <c r="D133" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
-      <c r="D134" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
-      <c r="D135" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
-      <c r="D136" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
-      <c r="D137" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
-      <c r="D138" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
-      <c r="D139" t="s">
+    <row r="160" spans="2:4">
+      <c r="D160" t="s">
         <v>262</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" s="9" customFormat="1">
-      <c r="A141" s="9" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
-      <c r="D142" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
-      <c r="B143" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
-      <c r="A144" s="10"/>
-      <c r="D144" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
-      <c r="B146" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
-      <c r="A147" s="10"/>
-      <c r="D147" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
-      <c r="E148" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
-      <c r="D149" s="7"/>
-    </row>
-    <row r="150" spans="1:5">
-      <c r="A150" s="10"/>
-      <c r="D150" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
-      <c r="A156" s="12"/>
-      <c r="B156" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="161" spans="4:4">
       <c r="D161" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
     </row>
     <row r="162" spans="4:4">
       <c r="D162" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="163" spans="4:4">
       <c r="D163" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
     </row>
     <row r="164" spans="4:4">
       <c r="D164" t="s">
-        <v>240</v>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="165" spans="4:4">
+      <c r="D165" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="166" spans="4:4">
+      <c r="D166" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="167" spans="4:4">
+      <c r="D167" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="168" spans="4:4">
+      <c r="D168" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="169" spans="4:4">
+      <c r="D169" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="170" spans="4:4">
+      <c r="D170" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="171" spans="4:4">
+      <c r="D171" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="172" spans="4:4">
+      <c r="D172" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" s="12"/>
+      <c r="B178" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="D183" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="D184" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="D185" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="D186" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421ABFA7-04AC-460D-8F95-5D3E39FB41EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D61E76-5E7F-4A55-B230-3344A42A15AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体図" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="301">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -1516,16 +1516,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>client secretが変わってしまっていたため修正</t>
-    <rPh sb="14" eb="15">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>シュウセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>クライアントID</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1568,6 +1558,36 @@
   </si>
   <si>
     <t>OK</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>export GOOGLE_OAUTH_CLIENT_ID="1011354473098-od5n1po1v94lfv87qesep52i11rht3m3.apps.googleusercontent.com"</t>
+  </si>
+  <si>
+    <t>python get_refresh_token.py</t>
+  </si>
+  <si>
+    <t>client secretをハードコードするパタン（緊急回避）</t>
+    <rPh sb="26" eb="28">
+      <t>キンキュウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カイヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クライアントシークレットを環境変数に設定</t>
+    <rPh sb="13" eb="17">
+      <t>カンキョウヘンスウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>export GOOGLE_OAUTH_CLIENT_SECRET="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"</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1843,13 +1863,13 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>585788</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>200026</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>257240</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>57584</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1887,14 +1907,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>33338</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>33338</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>223230</xdr:rowOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>223229</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1931,14 +1951,14 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>52387</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>52389</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>643017</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>190353</xdr:rowOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>190352</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1975,13 +1995,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>4762</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>61913</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>319087</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>51288</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2019,14 +2039,14 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>52387</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>219523</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>23847</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>5776</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>5777</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2063,14 +2083,14 @@
     <xdr:from>
       <xdr:col>33</xdr:col>
       <xdr:colOff>391327</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>4763</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>214367</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>128588</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2107,14 +2127,14 @@
     <xdr:from>
       <xdr:col>18</xdr:col>
       <xdr:colOff>42863</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>52388</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>323589</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3533,727 +3553,764 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89218E65-9CD0-49A4-A7F2-71B0476A86F1}">
-  <dimension ref="A1:T186"/>
+  <dimension ref="A1:T196"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="3" width="2.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="9" customFormat="1">
+    <row r="2" spans="1:5" s="9" customFormat="1">
       <c r="A2" s="9" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:5">
       <c r="D3" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:5">
       <c r="B4" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:5">
       <c r="A5" s="10"/>
       <c r="D5" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:5">
       <c r="B7" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:5">
       <c r="D8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:5">
       <c r="A9" s="10"/>
       <c r="D9" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:5">
       <c r="E10" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:5">
       <c r="D11" s="7"/>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:5">
       <c r="A12" s="10"/>
       <c r="D12" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:5">
       <c r="B14" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
-      <c r="A15" s="10"/>
+    <row r="15" spans="1:5">
       <c r="D15" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="10"/>
+      <c r="D16" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" s="10"/>
+      <c r="D17" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" s="10"/>
+      <c r="D18" t="s">
         <v>233</v>
       </c>
-      <c r="S15" t="s">
+      <c r="S18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="D19" t="s">
+        <v>231</v>
+      </c>
+      <c r="S19" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="S20" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
-      <c r="D16" t="s">
-        <v>231</v>
-      </c>
-      <c r="S16" t="s">
+    <row r="21" spans="1:19">
+      <c r="B21" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="D21" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
-      <c r="S17" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19">
-      <c r="B18" s="16" t="s">
+    <row r="23" spans="1:19">
+      <c r="A23" s="10"/>
+      <c r="D23" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" s="10"/>
+      <c r="B25" t="s">
         <v>295</v>
       </c>
-      <c r="D18" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19">
-      <c r="A20" s="10"/>
-      <c r="D20" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19">
-      <c r="A22" s="10"/>
-      <c r="B22" t="s">
-        <v>296</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="D25" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="18" customHeight="1"/>
-    <row r="24" spans="1:19" s="9" customFormat="1" ht="18" customHeight="1">
-      <c r="A24" s="9" t="s">
+    <row r="26" spans="1:19" ht="18" customHeight="1"/>
+    <row r="27" spans="1:19" s="9" customFormat="1" ht="18" customHeight="1">
+      <c r="A27" s="9" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
-      <c r="B25" t="s">
+    <row r="28" spans="1:19">
+      <c r="B28" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
-      <c r="A26" t="s">
+    <row r="29" spans="1:19">
+      <c r="A29" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
-      <c r="D27" t="s">
+    <row r="30" spans="1:19">
+      <c r="D30" t="s">
         <v>193</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19">
-      <c r="D28" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19">
-      <c r="A30" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:19">
       <c r="D31" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
+      <c r="A33" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="D34" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
-      <c r="A32" s="12"/>
-      <c r="D32" t="s">
+    <row r="35" spans="1:20">
+      <c r="A35" s="12"/>
+      <c r="D35" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
-      <c r="A34" t="s">
+    <row r="37" spans="1:20">
+      <c r="A37" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
-      <c r="D35" t="s">
+    <row r="38" spans="1:20">
+      <c r="D38" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="12"/>
-      <c r="D36" t="s">
+    <row r="39" spans="1:20">
+      <c r="A39" s="12"/>
+      <c r="D39" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="12"/>
-      <c r="D37" t="s">
+    <row r="40" spans="1:20">
+      <c r="A40" s="12"/>
+      <c r="D40" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="38" spans="1:20">
-      <c r="E38" t="s">
+    <row r="41" spans="1:20">
+      <c r="E41" t="s">
         <v>199</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G41" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
-      <c r="E39" t="s">
+    <row r="42" spans="1:20">
+      <c r="E42" t="s">
         <v>197</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G42" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="40" spans="1:20">
-      <c r="E40" t="s">
+    <row r="43" spans="1:20">
+      <c r="E43" t="s">
         <v>201</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G43" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:20">
-      <c r="A42" t="s">
+    <row r="45" spans="1:20">
+      <c r="A45" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="43" spans="1:20">
-      <c r="A43" s="12"/>
-      <c r="D43" t="s">
+    <row r="46" spans="1:20">
+      <c r="A46" s="12"/>
+      <c r="D46" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="44" spans="1:20">
-      <c r="T44" t="s">
+    <row r="47" spans="1:20">
+      <c r="T47" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="48" spans="1:20">
-      <c r="A48" s="12"/>
-      <c r="D48" t="s">
+    <row r="51" spans="1:4">
+      <c r="A51" s="12"/>
+      <c r="D51" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
-      <c r="D49" t="s">
+    <row r="52" spans="1:4">
+      <c r="D52" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
-      <c r="D50" t="s">
+    <row r="53" spans="1:4">
+      <c r="D53" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
-      <c r="D51" t="s">
+    <row r="54" spans="1:4">
+      <c r="D54" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
-      <c r="A53" t="s">
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="D55" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="D56" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="D57" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="D58" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="D59" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="D60" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="D61" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="D62" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="D63" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="D64" t="s">
         <v>174</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="D63" s="13" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="12"/>
-      <c r="D64" s="7" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="D65" s="13" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="D66" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="12"/>
+      <c r="D67" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="D68" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="D69" s="13" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
-      <c r="D67" s="13" t="s">
+    <row r="70" spans="1:4">
+      <c r="D70" s="13" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
-      <c r="D68" s="7"/>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" t="s">
+    <row r="71" spans="1:4">
+      <c r="D71" s="7"/>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="D71" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="12"/>
-      <c r="D72" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="12"/>
-      <c r="D73" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="D74" t="s">
-        <v>229</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="12"/>
+      <c r="D75" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:4">
+      <c r="A76" s="12"/>
       <c r="D76" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="D77" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="D79" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="D80" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
-      <c r="B79" s="12"/>
-      <c r="D79" t="s">
+    <row r="82" spans="2:19">
+      <c r="B82" s="12"/>
+      <c r="D82" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
-      <c r="B80" s="12"/>
-      <c r="D80" t="s">
+    <row r="83" spans="2:19">
+      <c r="B83" s="12"/>
+      <c r="D83" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="4:19">
-      <c r="E81" t="s">
+    <row r="84" spans="2:19">
+      <c r="E84" t="s">
         <v>235</v>
       </c>
-      <c r="R81" t="s">
+      <c r="R84" t="s">
         <v>234</v>
       </c>
-      <c r="S81" t="s">
+      <c r="S84" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="4:19">
-      <c r="D87" t="s">
+    <row r="90" spans="2:19">
+      <c r="D90" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="88" spans="4:19">
-      <c r="E88" t="s">
+    <row r="91" spans="2:19">
+      <c r="E91" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="92" spans="2:19">
+      <c r="E92" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="93" spans="2:19">
+      <c r="E93" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="94" spans="2:19">
+      <c r="E94" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="E98" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="E99" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="89" spans="4:19">
-      <c r="E89" t="s">
+      <c r="G99" t="s">
         <v>286</v>
       </c>
-      <c r="G89" t="s">
+    </row>
+    <row r="100" spans="1:7">
+      <c r="E100" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="90" spans="4:19">
-      <c r="E90" t="s">
+      <c r="G100" t="s">
         <v>288</v>
       </c>
-      <c r="G90" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="12"/>
-      <c r="D98" t="s">
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="12"/>
+      <c r="D108" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" t="s">
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="12"/>
-      <c r="D102" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="D103" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="12"/>
-      <c r="D105" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="D106" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="D107" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="D108" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="D109" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="D110" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:7">
       <c r="A112" s="12"/>
       <c r="D112" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" t="s">
-        <v>182</v>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="D113" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="12"/>
+      <c r="D115" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="D116" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="D117" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="D118" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="D119" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="D120" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="12"/>
+      <c r="D122" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="D126" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
-      <c r="E117" t="s">
+    <row r="127" spans="1:5">
+      <c r="E127" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
-      <c r="E118" t="s">
+    <row r="128" spans="1:5">
+      <c r="E128" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
-      <c r="E119" t="s">
+    <row r="129" spans="1:5">
+      <c r="E129" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
-      <c r="E120" t="s">
+    <row r="130" spans="1:5">
+      <c r="E130" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
-      <c r="E121" t="s">
+    <row r="131" spans="1:5">
+      <c r="E131" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
-      <c r="E122" t="s">
+    <row r="132" spans="1:5">
+      <c r="E132" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
-      <c r="E123" t="s">
+    <row r="133" spans="1:5">
+      <c r="E133" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
-      <c r="D125" t="s">
+    <row r="135" spans="1:5">
+      <c r="D135" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="12"/>
-      <c r="D126" t="s">
+    <row r="136" spans="1:5">
+      <c r="A136" s="12"/>
+      <c r="D136" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
-      <c r="A127" s="12"/>
-      <c r="D127" t="s">
+    <row r="137" spans="1:5">
+      <c r="A137" s="12"/>
+      <c r="D137" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
-      <c r="D128" t="s">
+    <row r="138" spans="1:5">
+      <c r="D138" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
-      <c r="A130" t="s">
+    <row r="140" spans="1:5">
+      <c r="A140" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
-      <c r="A132" s="12"/>
-      <c r="D132" t="s">
+    <row r="142" spans="1:5">
+      <c r="A142" s="12"/>
+      <c r="D142" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
-      <c r="A134" t="s">
+    <row r="144" spans="1:5">
+      <c r="A144" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
-      <c r="A136" s="14"/>
-      <c r="D136" t="s">
+    <row r="146" spans="1:4">
+      <c r="A146" s="14"/>
+      <c r="D146" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
-      <c r="A137" s="14"/>
-      <c r="D137" t="s">
+    <row r="147" spans="1:4">
+      <c r="A147" s="14"/>
+      <c r="D147" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
-      <c r="A138" s="14"/>
-      <c r="D138" t="s">
+    <row r="148" spans="1:4">
+      <c r="A148" s="14"/>
+      <c r="D148" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="140" spans="1:4" s="9" customFormat="1"/>
-    <row r="141" spans="1:4">
-      <c r="A141" t="s">
+    <row r="150" spans="1:4" s="9" customFormat="1"/>
+    <row r="151" spans="1:4">
+      <c r="A151" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
-      <c r="D143" t="s">
+    <row r="153" spans="1:4">
+      <c r="D153" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
-      <c r="D144" t="s">
+    <row r="154" spans="1:4">
+      <c r="D154" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
-      <c r="D145" t="s">
+    <row r="155" spans="1:4">
+      <c r="D155" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="D146" t="s">
+    <row r="156" spans="1:4">
+      <c r="D156" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="148" spans="2:4">
-      <c r="D148" t="s">
+    <row r="158" spans="1:4">
+      <c r="D158" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="D149" t="s">
+    <row r="159" spans="1:4">
+      <c r="D159" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="151" spans="2:4">
-      <c r="D151" t="s">
+    <row r="161" spans="2:4">
+      <c r="D161" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="152" spans="2:4">
-      <c r="D152" t="s">
+    <row r="162" spans="2:4">
+      <c r="D162" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
-      <c r="D153" t="s">
+    <row r="163" spans="2:4">
+      <c r="D163" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
-      <c r="D154" t="s">
+    <row r="164" spans="2:4">
+      <c r="D164" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
-      <c r="D155" t="s">
+    <row r="165" spans="2:4">
+      <c r="D165" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
-      <c r="D156" t="s">
+    <row r="166" spans="2:4">
+      <c r="D166" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="D157" t="s">
+    <row r="167" spans="2:4">
+      <c r="D167" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="158" spans="2:4">
-      <c r="B158" t="s">
+    <row r="168" spans="2:4">
+      <c r="B168" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="C159" t="s">
+    <row r="169" spans="2:4">
+      <c r="C169" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="160" spans="2:4">
-      <c r="D160" t="s">
+    <row r="170" spans="2:4">
+      <c r="D170" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="161" spans="4:4">
-      <c r="D161" t="s">
+    <row r="171" spans="2:4">
+      <c r="D171" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="162" spans="4:4">
-      <c r="D162" t="s">
+    <row r="172" spans="2:4">
+      <c r="D172" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="163" spans="4:4">
-      <c r="D163" t="s">
+    <row r="173" spans="2:4">
+      <c r="D173" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="164" spans="4:4">
-      <c r="D164" t="s">
+    <row r="174" spans="2:4">
+      <c r="D174" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="165" spans="4:4">
-      <c r="D165" t="s">
+    <row r="175" spans="2:4">
+      <c r="D175" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="166" spans="4:4">
-      <c r="D166" t="s">
+    <row r="176" spans="2:4">
+      <c r="D176" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="167" spans="4:4">
-      <c r="D167" t="s">
+    <row r="177" spans="1:4">
+      <c r="D177" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="168" spans="4:4">
-      <c r="D168" t="s">
+    <row r="178" spans="1:4">
+      <c r="D178" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="169" spans="4:4">
-      <c r="D169" t="s">
+    <row r="179" spans="1:4">
+      <c r="D179" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="170" spans="4:4">
-      <c r="D170" t="s">
+    <row r="180" spans="1:4">
+      <c r="D180" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="171" spans="4:4">
-      <c r="D171" t="s">
+    <row r="181" spans="1:4">
+      <c r="D181" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="172" spans="4:4">
-      <c r="D172" t="s">
+    <row r="182" spans="1:4">
+      <c r="D182" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="178" spans="1:4">
-      <c r="A178" s="12"/>
-      <c r="B178" t="s">
+    <row r="188" spans="1:4">
+      <c r="A188" s="12"/>
+      <c r="B188" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="183" spans="1:4">
-      <c r="D183" t="s">
+    <row r="193" spans="4:4">
+      <c r="D193" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="184" spans="1:4">
-      <c r="D184" t="s">
+    <row r="194" spans="4:4">
+      <c r="D194" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="185" spans="1:4">
-      <c r="D185" t="s">
+    <row r="195" spans="4:4">
+      <c r="D195" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="186" spans="1:4">
-      <c r="D186" t="s">
+    <row r="196" spans="4:4">
+      <c r="D196" t="s">
         <v>239</v>
       </c>
     </row>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D61E76-5E7F-4A55-B230-3344A42A15AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939B0687-4F1D-4072-9E14-B8C5A9BCE125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体図" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="304">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -1588,6 +1588,18 @@
   </si>
   <si>
     <t>export GOOGLE_OAUTH_CLIENT_SECRET="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"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>export GOOGLE_OAUTH_CLIENT_ID="1011354473098-od5n1po1v94lfv87qesep52i11rht3m3.apps.googleusercontent.com"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>$env:GOOGLE_OAUTH_CLIENT_ID="1011354473098-od5n1po1v94lfv87qesep52i11rht3m3.apps.googleusercontent.com"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>$env:GOOGLE_OAUTH_CLIENT_SECRET="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"</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3559,82 +3571,88 @@
     <col min="1" max="3" width="2.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="9" customFormat="1">
+    <row r="2" spans="1:16" s="9" customFormat="1">
       <c r="A2" s="9" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:16">
       <c r="D3" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:16">
       <c r="B4" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:16">
       <c r="A5" s="10"/>
       <c r="D5" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:16">
       <c r="B7" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:16">
       <c r="D8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:16">
       <c r="A9" s="10"/>
       <c r="D9" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:16">
       <c r="E10" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:16">
       <c r="D11" s="7"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:16">
       <c r="A12" s="10"/>
       <c r="D12" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:16">
       <c r="B14" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:16">
       <c r="D15" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:16">
       <c r="A16" s="10"/>
       <c r="D16" t="s">
-        <v>296</v>
+        <v>301</v>
+      </c>
+      <c r="P16" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="10"/>
       <c r="D17" t="s">
         <v>300</v>
+      </c>
+      <c r="P17" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="1:19">

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939B0687-4F1D-4072-9E14-B8C5A9BCE125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C297935A-6796-47C9-95E8-7758F8F87942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体図" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="308">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -923,16 +923,6 @@
   </si>
   <si>
     <t>sam</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>共通CRUD関数, api, mcp</t>
-    <rPh sb="0" eb="2">
-      <t>キョウツウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>カンスウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1404,12 +1394,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>共有モジュールコピー</t>
-  </si>
-  <si>
-    <t>デプロイ実行</t>
-  </si>
-  <si>
     <t>cd task-agent</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1499,16 +1483,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>GoogleDriveアクセス用トークン更新</t>
-    <rPh sb="15" eb="16">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>2026.8.10修正</t>
     <rPh sb="9" eb="11">
       <t>シュウセイ</t>
@@ -1553,10 +1527,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ダメ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>OK</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1600,6 +1570,51 @@
   </si>
   <si>
     <t>$env:GOOGLE_OAUTH_CLIENT_SECRET="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"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2026.8.12</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(backend) 共通CRUD関数, api, mcp</t>
+    <rPh sb="10" eb="12">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(frontend)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(db)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>agent</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>agentcore, skill</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GoogleDriveアクセス用トークン</t>
+    <rPh sb="15" eb="16">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>共有モジュール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1826,13 +1841,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>138</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>19051</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>476330</xdr:colOff>
-      <xdr:row>147</xdr:row>
+      <xdr:row>149</xdr:row>
       <xdr:rowOff>188078</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2626,7 +2641,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M193"/>
+  <dimension ref="A1:M195"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="2" width="2.5625" customWidth="1"/>
@@ -2637,7 +2652,7 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2677,15 +2692,21 @@
         <v>153</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>277</v>
+    <row r="7" spans="1:10" s="15" customFormat="1">
+      <c r="A7" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="D8" s="2" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="9" spans="1:10">
       <c r="C9" t="s">
@@ -2694,77 +2715,77 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D11" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>24</v>
+      <c r="D12" s="2" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="C14" t="s">
+    <row r="15" spans="1:10">
+      <c r="C15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
-      <c r="C15" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="B17" s="2" t="s">
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="C18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="B19" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="C19" s="2"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="C20" s="2"/>
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5">
@@ -2796,135 +2817,127 @@
       <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" s="9" customFormat="1">
-      <c r="A29" s="11" t="s">
+      <c r="C28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="C29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="9" customFormat="1">
+      <c r="A31" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="B30" t="s">
+    <row r="32" spans="1:5">
+      <c r="B32" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="C31" t="s">
+    <row r="33" spans="1:6">
+      <c r="C33" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="C33" s="2" t="s">
+    <row r="35" spans="1:6">
+      <c r="A35" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
-      <c r="B34" t="s">
+    <row r="36" spans="1:6">
+      <c r="B36" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="C35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" s="9" customFormat="1">
-      <c r="A36" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="C37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" s="9" customFormat="1">
+      <c r="A38" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="C39" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="D38" t="s">
+    <row r="40" spans="1:6">
+      <c r="D40" t="s">
         <v>32</v>
       </c>
-      <c r="F38" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="D39" t="s">
+      <c r="F40" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="D41" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
-      <c r="C40" t="s">
+    <row r="42" spans="1:6">
+      <c r="C42" t="s">
         <v>8</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E42" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
-      <c r="D41" s="3" t="s">
+    <row r="43" spans="1:6">
+      <c r="D43" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="D42" s="3" t="s">
+    <row r="44" spans="1:6">
+      <c r="D44" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="C44" t="s">
+    <row r="46" spans="1:6">
+      <c r="C46" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
-      <c r="D45" t="s">
+    <row r="47" spans="1:6">
+      <c r="D47" t="s">
         <v>10</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F47" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="D46" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="D47" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="D48" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F48" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="D49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="D49" t="s">
-        <v>17</v>
-      </c>
-      <c r="F49" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="50" spans="2:6">
       <c r="D50" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
@@ -2932,341 +2945,341 @@
     </row>
     <row r="51" spans="2:6">
       <c r="D51" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="2:6">
       <c r="D52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="D53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6">
+      <c r="D54" t="s">
         <v>22</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F54" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
-      <c r="B54" t="s">
+    <row r="56" spans="2:6">
+      <c r="B56" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
-      <c r="D55" t="s">
+    <row r="57" spans="2:6">
+      <c r="D57" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
-      <c r="D56" t="s">
+    <row r="58" spans="2:6">
+      <c r="D58" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="C58" t="s">
+    <row r="60" spans="2:6">
+      <c r="C60" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="2:6">
-      <c r="C59" t="s">
+    <row r="61" spans="2:6">
+      <c r="C61" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" t="s">
+    <row r="63" spans="2:6">
+      <c r="B63" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
-      <c r="C62" t="s">
+    <row r="64" spans="2:6">
+      <c r="C64" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="D63" t="s">
+    <row r="65" spans="4:4">
+      <c r="D65" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
-      <c r="D64" t="s">
+    <row r="66" spans="4:4">
+      <c r="D66" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
-      <c r="D65" t="s">
+    <row r="67" spans="4:4">
+      <c r="D67" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
-      <c r="D66" t="s">
+    <row r="68" spans="4:4">
+      <c r="D68" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
-      <c r="D67" t="s">
+    <row r="69" spans="4:4">
+      <c r="D69" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
-      <c r="D68" t="s">
+    <row r="70" spans="4:4">
+      <c r="D70" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
-      <c r="D69" t="s">
+    <row r="71" spans="4:4">
+      <c r="D71" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
-      <c r="D70" t="s">
+    <row r="72" spans="4:4">
+      <c r="D72" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
-      <c r="D71" t="s">
+    <row r="73" spans="4:4">
+      <c r="D73" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
-      <c r="D72" t="s">
+    <row r="74" spans="4:4">
+      <c r="D74" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
-      <c r="D73" t="s">
+    <row r="75" spans="4:4">
+      <c r="D75" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
-      <c r="D74" t="s">
+    <row r="76" spans="4:4">
+      <c r="D76" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
-      <c r="D75" t="s">
+    <row r="77" spans="4:4">
+      <c r="D77" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
-      <c r="D76" t="s">
+    <row r="78" spans="4:4">
+      <c r="D78" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
-      <c r="A79" t="s">
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
-      <c r="C80" t="s">
+    <row r="82" spans="1:4">
+      <c r="C82" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
-      <c r="D81" t="s">
+    <row r="83" spans="1:4">
+      <c r="D83" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
-      <c r="D82" t="s">
+    <row r="84" spans="1:4">
+      <c r="D84" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
-      <c r="C83" t="s">
+    <row r="85" spans="1:4">
+      <c r="C85" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="D84" s="2" t="s">
+    <row r="86" spans="1:4">
+      <c r="A86" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="D85" s="2" t="s">
+    <row r="87" spans="1:4">
+      <c r="A87" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
-      <c r="D86" t="s">
+    <row r="88" spans="1:4">
+      <c r="D88" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
-      <c r="D87" s="3" t="s">
+    <row r="89" spans="1:4">
+      <c r="D89" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="D88" s="2" t="s">
+    <row r="90" spans="1:4">
+      <c r="A90" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="21.75">
-      <c r="C90" s="4" t="s">
+    <row r="92" spans="1:4" ht="21.75">
+      <c r="C92" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
-      <c r="C91" t="s">
+    <row r="93" spans="1:4">
+      <c r="C93" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
-      <c r="C92" s="5" t="s">
+    <row r="94" spans="1:4">
+      <c r="C94" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
-      <c r="C93" s="6" t="s">
+    <row r="95" spans="1:4">
+      <c r="C95" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
-      <c r="C94" s="6" t="s">
+    <row r="96" spans="1:4">
+      <c r="C96" s="6" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="C95" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="C96" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="97" spans="1:13">
       <c r="C97" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13">
+      <c r="C98" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13">
+      <c r="C99" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="98" spans="1:13">
-      <c r="C98" s="6" t="s">
+    <row r="100" spans="1:13">
+      <c r="C100" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="100" spans="1:13" s="9" customFormat="1">
-      <c r="A100" s="9" t="s">
+    <row r="102" spans="1:13" s="9" customFormat="1">
+      <c r="A102" s="9" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13">
-      <c r="B101" t="s">
-        <v>32</v>
-      </c>
-      <c r="F101" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13">
-      <c r="B102" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="103" spans="1:13">
       <c r="B103" t="s">
+        <v>32</v>
+      </c>
+      <c r="F103" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13">
+      <c r="B104" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13">
+      <c r="B105" t="s">
         <v>65</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E105" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="105" spans="1:13">
-      <c r="C105" t="s">
+    <row r="107" spans="1:13">
+      <c r="C107" t="s">
         <v>36</v>
       </c>
-      <c r="M105" t="s">
+      <c r="M107" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="106" spans="1:13">
-      <c r="D106" s="2" t="s">
+    <row r="108" spans="1:13">
+      <c r="D108" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M106" t="s">
+      <c r="M108" t="s">
         <v>142</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13">
-      <c r="D107" t="s">
-        <v>26</v>
-      </c>
-      <c r="M107" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13">
-      <c r="D108" t="s">
-        <v>52</v>
-      </c>
-      <c r="M108" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="109" spans="1:13">
       <c r="D109" t="s">
+        <v>26</v>
+      </c>
+      <c r="M109" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13">
+      <c r="D110" t="s">
+        <v>52</v>
+      </c>
+      <c r="M110" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13">
+      <c r="D111" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="110" spans="1:13">
-      <c r="E110" t="s">
+    <row r="112" spans="1:13">
+      <c r="E112" t="s">
         <v>10</v>
       </c>
-      <c r="G110" t="s">
+      <c r="G112" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13">
-      <c r="E111" t="s">
-        <v>13</v>
-      </c>
-      <c r="G111" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13">
-      <c r="E112" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G112" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="113" spans="3:8">
       <c r="E113" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G113" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="3:8">
+      <c r="E114" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G114" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="114" spans="3:8">
-      <c r="E114" t="s">
-        <v>17</v>
-      </c>
-      <c r="G114" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="115" spans="3:8">
       <c r="E115" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G115" t="s">
         <v>14</v>
@@ -3274,289 +3287,305 @@
     </row>
     <row r="116" spans="3:8">
       <c r="E116" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G116" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117" spans="3:8">
       <c r="E117" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G117" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118" spans="3:8">
       <c r="E118" t="s">
+        <v>20</v>
+      </c>
+      <c r="G118" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="119" spans="3:8">
+      <c r="E119" t="s">
+        <v>22</v>
+      </c>
+      <c r="G119" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" spans="3:8">
+      <c r="E120" t="s">
         <v>68</v>
       </c>
-      <c r="H118" t="s">
+      <c r="H120" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="119" spans="3:8">
-      <c r="C119" t="s">
+    <row r="121" spans="3:8">
+      <c r="C121" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="120" spans="3:8">
-      <c r="D120" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="121" spans="3:8">
-      <c r="D121" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="122" spans="3:8">
       <c r="D122" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="123" spans="3:8">
       <c r="D123" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="124" spans="3:8">
+      <c r="D124" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="125" spans="3:8">
+      <c r="D125" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="129" spans="1:5" s="9" customFormat="1">
-      <c r="A129" s="9" t="s">
+    <row r="131" spans="1:5" s="9" customFormat="1">
+      <c r="A131" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E129" s="9" t="s">
+      <c r="E131" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
-      <c r="D130" t="s">
+    <row r="132" spans="1:5">
+      <c r="D132" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="E131" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
-      <c r="E132" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="E133" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="E134" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="E135" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="E136" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="E137" t="s">
-        <v>74</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="E138" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="E139" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="E140" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="E141" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="E142" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="E143" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="E144" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="145" spans="5:5">
+      <c r="E145" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="151" spans="5:5">
-      <c r="E151" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="152" spans="5:5">
-      <c r="E152" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="153" spans="5:5">
       <c r="E153" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="154" spans="5:5">
       <c r="E154" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="155" spans="5:5">
       <c r="E155" t="s">
-        <v>84</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="156" spans="5:5">
+      <c r="E156" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="157" spans="5:5">
       <c r="E157" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="158" spans="5:5">
-      <c r="E158" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="159" spans="5:5">
       <c r="E159" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="160" spans="5:5">
       <c r="E160" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="161" spans="4:5">
       <c r="E161" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="162" spans="4:5">
       <c r="E162" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="163" spans="4:5">
+      <c r="E163" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="164" spans="4:5">
       <c r="E164" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="166" spans="4:5">
+      <c r="E166" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="165" spans="4:5">
-      <c r="E165" t="s">
+    <row r="167" spans="4:5">
+      <c r="E167" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="167" spans="4:5">
-      <c r="D167" t="s">
+    <row r="169" spans="4:5">
+      <c r="D169" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="168" spans="4:5">
-      <c r="E168" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="169" spans="4:5">
-      <c r="E169" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="170" spans="4:5">
       <c r="E170" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="171" spans="4:5">
       <c r="E171" t="s">
-        <v>94</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="172" spans="4:5">
+      <c r="E172" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="173" spans="4:5">
       <c r="E173" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="175" spans="4:5">
       <c r="E175" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="E177" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="176" spans="4:5">
-      <c r="E176" t="s">
+    <row r="178" spans="1:5">
+      <c r="E178" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="178" spans="1:5" s="9" customFormat="1">
-      <c r="A178" s="11" t="s">
+    <row r="180" spans="1:5" s="9" customFormat="1">
+      <c r="A180" s="11" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
-      <c r="C180" t="s">
+    <row r="182" spans="1:5">
+      <c r="C182" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
-      <c r="E181" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
-      <c r="E182" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="E183" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="E184" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="E185" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
-      <c r="C185" t="s">
+    <row r="187" spans="1:5">
+      <c r="C187" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
-      <c r="A187" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="C187" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C189" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="C191" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="193" spans="1:3">
-      <c r="A193" t="s">
+    <row r="195" spans="1:3">
+      <c r="A195" t="s">
         <v>107</v>
       </c>
-      <c r="C193" t="s">
+      <c r="C195" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="E96" r:id="rId1" xr:uid="{6779DE2A-DCC0-4F58-8418-AF9B609FD587}"/>
+    <hyperlink ref="E98" r:id="rId1" xr:uid="{6779DE2A-DCC0-4F58-8418-AF9B609FD587}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
@@ -3573,33 +3602,41 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" s="9" customFormat="1">
-      <c r="A2" s="9" t="s">
-        <v>266</v>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="15" customFormat="1">
+      <c r="A2" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="D3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="B4" t="s">
-        <v>267</v>
+      <c r="B4" s="2" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="10"/>
+      <c r="A5" s="10" t="s">
+        <v>264</v>
+      </c>
       <c r="D5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="B7" t="s">
-        <v>268</v>
+      <c r="B7" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -3608,287 +3645,301 @@
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="10"/>
+      <c r="A9" s="10" t="s">
+        <v>264</v>
+      </c>
       <c r="D9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="E10" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="10"/>
+      <c r="A12" s="10" t="s">
+        <v>264</v>
+      </c>
       <c r="D12" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="B14" t="s">
-        <v>283</v>
+      <c r="B14" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="D15" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="10"/>
+      <c r="A16" s="10" t="s">
+        <v>264</v>
+      </c>
       <c r="D16" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="P16" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="10"/>
+      <c r="A17" s="10" t="s">
+        <v>264</v>
+      </c>
       <c r="D17" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="P17" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="10"/>
+      <c r="A18" s="10" t="s">
+        <v>264</v>
+      </c>
       <c r="D18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S18" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:19">
       <c r="D19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="S19" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20" spans="1:19">
       <c r="S20" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="C21" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="D21" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="D23" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C25" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="21" spans="1:19">
-      <c r="B21" s="16" t="s">
-        <v>294</v>
-      </c>
-      <c r="D21" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19">
-      <c r="A23" s="10"/>
-      <c r="D23" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19">
-      <c r="A25" s="10"/>
-      <c r="B25" t="s">
-        <v>295</v>
-      </c>
       <c r="D25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="18" customHeight="1"/>
     <row r="27" spans="1:19" s="9" customFormat="1" ht="18" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" spans="1:19">
       <c r="B28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:19">
       <c r="A29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:19">
       <c r="D30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:19">
       <c r="D31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:20">
       <c r="A33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:20">
       <c r="D34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:20">
       <c r="A35" s="12"/>
       <c r="D35" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:20">
       <c r="D38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39" spans="1:20">
       <c r="A39" s="12"/>
       <c r="D39" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" spans="1:20">
       <c r="A40" s="12"/>
       <c r="D40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:20">
       <c r="E41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G41" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:20">
       <c r="E42" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G42" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:20">
       <c r="E43" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G43" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45" spans="1:20">
       <c r="A45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:20">
       <c r="A46" s="12"/>
       <c r="D46" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="47" spans="1:20">
       <c r="T47" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="12"/>
       <c r="D51" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="D52" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="D53" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="D54" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="D58" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="D59" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="D60" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="D61" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="D62" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="D63" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="D64" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="D66" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="12"/>
       <c r="D67" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="D68" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="D69" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="D70" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3896,440 +3947,440 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="D74" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="12"/>
       <c r="D75" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="12"/>
       <c r="D76" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="D77" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="D79" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="D80" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="82" spans="2:19">
       <c r="B82" s="12"/>
       <c r="D82" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="83" spans="2:19">
       <c r="B83" s="12"/>
       <c r="D83" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="2:19">
       <c r="E84" t="s">
+        <v>234</v>
+      </c>
+      <c r="R84" t="s">
+        <v>233</v>
+      </c>
+      <c r="S84" t="s">
         <v>235</v>
-      </c>
-      <c r="R84" t="s">
-        <v>234</v>
-      </c>
-      <c r="S84" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="90" spans="2:19">
       <c r="D90" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="91" spans="2:19">
       <c r="E91" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="92" spans="2:19">
       <c r="E92" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="93" spans="2:19">
       <c r="E93" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="94" spans="2:19">
       <c r="E94" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="E98" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="E99" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G99" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="100" spans="1:7">
       <c r="E100" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="G100" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="12"/>
       <c r="D108" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="12"/>
       <c r="D112" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="D113" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="12"/>
       <c r="D115" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="D116" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="D117" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="D118" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="D119" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="D120" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="12"/>
       <c r="D122" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="D126" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="E127" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="E128" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="E129" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="E130" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="E131" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="E132" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="E133" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="D135" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="12"/>
       <c r="D136" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="12"/>
       <c r="D137" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="D138" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="12"/>
       <c r="D142" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="14"/>
       <c r="D146" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="14"/>
       <c r="D147" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="14"/>
       <c r="D148" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="150" spans="1:4" s="9" customFormat="1"/>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="D153" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="154" spans="1:4">
       <c r="D154" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="155" spans="1:4">
       <c r="D155" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="D156" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="158" spans="1:4">
       <c r="D158" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="D159" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="D161" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="D162" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="163" spans="2:4">
       <c r="D163" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="164" spans="2:4">
       <c r="D164" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="165" spans="2:4">
       <c r="D165" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="166" spans="2:4">
       <c r="D166" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="167" spans="2:4">
       <c r="D167" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="168" spans="2:4">
       <c r="B168" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="C169" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="D170" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="171" spans="2:4">
       <c r="D171" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="172" spans="2:4">
       <c r="D172" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="173" spans="2:4">
       <c r="D173" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="174" spans="2:4">
       <c r="D174" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="175" spans="2:4">
       <c r="D175" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="176" spans="2:4">
       <c r="D176" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="D177" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="D178" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="D179" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="D180" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="D181" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="182" spans="1:4">
       <c r="D182" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="12"/>
       <c r="B188" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="193" spans="4:4">
       <c r="D193" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="194" spans="4:4">
       <c r="D194" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="195" spans="4:4">
       <c r="D195" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="196" spans="4:4">
       <c r="D196" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/setup手順.xlsx
+++ b/setup手順.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\taskmanager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C297935A-6796-47C9-95E8-7758F8F87942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96CADD1-8010-4B66-ACED-C549B6EA9BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="309">
   <si>
     <t>cd C:\Users\woody\0woodyprojects\Jakalulu\04_Projects\AMOROHOUS\taskmanager</t>
   </si>
@@ -1615,6 +1615,13 @@
   </si>
   <si>
     <t>NG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>毎回不要</t>
+    <rPh sb="0" eb="4">
+      <t>マイカイフヨウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3659,6 +3666,9 @@
     </row>
     <row r="11" spans="1:16">
       <c r="D11" s="7"/>
+      <c r="E11" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="10" t="s">
